--- a/salida/mrp/MRP_MP.xlsx
+++ b/salida/mrp/MRP_MP.xlsx
@@ -97,17 +97,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF8B8B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF8B8B"/>
       </patternFill>
     </fill>
   </fills>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>3.764</v>
+        <v>3.914</v>
       </c>
       <c r="C9" s="16">
         <f>$B9*'Demanda'!B10</f>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>4.7</v>
+        <v>4.879</v>
       </c>
       <c r="C10" s="16">
         <f>$B10*'Demanda'!B11</f>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>5.264</v>
+        <v>5.457</v>
       </c>
       <c r="C11" s="16">
         <f>$B11*'Demanda'!B12</f>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>5.857</v>
+        <v>6.071</v>
       </c>
       <c r="C12" s="16">
         <f>$B12*'Demanda'!B13</f>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="B17" s="27" t="n">
-        <v>3.764</v>
+        <v>3.914</v>
       </c>
       <c r="C17" s="16">
         <f>$B17*'Demanda'!B31</f>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="B18" s="27" t="n">
-        <v>4.7</v>
+        <v>4.879</v>
       </c>
       <c r="C18" s="16">
         <f>$B18*'Demanda'!B32</f>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B19" s="27" t="n">
-        <v>5.264</v>
+        <v>5.457</v>
       </c>
       <c r="C19" s="16">
         <f>$B19*'Demanda'!B33</f>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="B20" s="27" t="n">
-        <v>5.857</v>
+        <v>6.071</v>
       </c>
       <c r="C20" s="16">
         <f>$B20*'Demanda'!B34</f>
@@ -9416,7 +9416,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.144 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.107 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.393 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.400 de largo desarrollado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -9550,7 +9550,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.603 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.674 de largo desarrollado</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 224 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.915 de largo desarrollado</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -9684,7 +9684,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 298 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 224 de largo desarrollado</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 458 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 298 de largo desarrollado</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 895 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 458 de largo desarrollado</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -22379,27 +22379,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Chapa LAC 1500 × 3000 e=4,75</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Materia prima</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Pradecon S.A.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -22445,10 +22445,10 @@
         <v/>
       </c>
       <c r="AQ20" s="22" t="n">
-        <v>41.925</v>
+        <v>55.953</v>
       </c>
       <c r="AR20" s="22" t="n">
-        <v>55.947</v>
+        <v>55.91</v>
       </c>
     </row>
     <row r="21">
@@ -23152,27 +23152,27 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Planchuela SAE 1010 30 × 3</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>barra 6 m</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>Materia prima</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>Hierros Parrotta</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -23231,27 +23231,27 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>Planchuela SAE 1010 40 × 4</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>barra 6 m</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>Materia prima</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>Hierros Parrotta</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -23304,27 +23304,27 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Recorte de chapa LAC e=3,2 para el apoyo plegado</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>Materia prima</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>Pradecon S.A.</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -23462,27 +23462,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Redondo liso SAE 1010 Ø8</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>barra 6 m</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>Materia prima</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>Hierros Parrotta</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -23528,10 +23528,10 @@
         <v/>
       </c>
       <c r="AQ35" s="22" t="n">
-        <v>0.1089</v>
+        <v>0.128</v>
       </c>
       <c r="AR35" s="22" t="n">
-        <v>0.1265</v>
+        <v>0.1478</v>
       </c>
     </row>
     <row r="36">
@@ -25028,7 +25028,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.144 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.107 de largo desarrollado</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -25091,14 +25091,14 @@
         <f>SUMPRODUCT($AK57:$AR57,$AK$14:$AR$14)*IF($E57="CABA",'Parametros'!K$7,IF($E57="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP57" s="22" t="n">
+      <c r="AO57" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.393 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.400 de largo desarrollado</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -25161,14 +25161,14 @@
         <f>SUMPRODUCT($AK58:$AR58,$AK$14:$AR$14)*IF($E58="CABA",'Parametros'!K$7,IF($E58="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ58" s="22" t="n">
+      <c r="AP58" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.603 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.674 de largo desarrollado</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -25231,14 +25231,14 @@
         <f>SUMPRODUCT($AK59:$AR59,$AK$14:$AR$14)*IF($E59="CABA",'Parametros'!K$7,IF($E59="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR59" s="22" t="n">
+      <c r="AQ59" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 224 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.915 de largo desarrollado</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -25301,14 +25301,14 @@
         <f>SUMPRODUCT($AK60:$AR60,$AK$14:$AR$14)*IF($E60="CABA",'Parametros'!K$7,IF($E60="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL60" s="22" t="n">
+      <c r="AR60" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 298 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 224 de largo desarrollado</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -25371,14 +25371,14 @@
         <f>SUMPRODUCT($AK61:$AR61,$AK$14:$AR$14)*IF($E61="CABA",'Parametros'!K$7,IF($E61="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM61" s="22" t="n">
+      <c r="AL61" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 458 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 298 de largo desarrollado</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -25441,14 +25441,14 @@
         <f>SUMPRODUCT($AK62:$AR62,$AK$14:$AR$14)*IF($E62="CABA",'Parametros'!K$7,IF($E62="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN62" s="22" t="n">
+      <c r="AM62" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 895 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 458 de largo desarrollado</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -25511,32 +25511,32 @@
         <f>SUMPRODUCT($AK63:$AR63,$AK$14:$AR$14)*IF($E63="CABA",'Parametros'!K$7,IF($E63="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO63" s="22" t="n">
+      <c r="AN63" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>Manómetro — Ø28 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
         </is>
       </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B64" s="25" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
+      <c r="C64" s="25" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D64" s="24" t="inlineStr">
+      <c r="D64" s="25" t="inlineStr">
         <is>
           <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
-      <c r="E64" s="24" t="inlineStr">
+      <c r="E64" s="25" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -25586,27 +25586,27 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>Manómetro — Ø38 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
         </is>
       </c>
-      <c r="B65" s="24" t="inlineStr">
+      <c r="B65" s="25" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="C65" s="25" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D65" s="24" t="inlineStr">
+      <c r="D65" s="25" t="inlineStr">
         <is>
           <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
-      <c r="E65" s="24" t="inlineStr">
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -25662,27 +25662,27 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="25" t="inlineStr">
         <is>
           <t>Manómetro — Ø50 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
         </is>
       </c>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B66" s="25" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C66" s="24" t="inlineStr">
+      <c r="C66" s="25" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D66" s="24" t="inlineStr">
+      <c r="D66" s="25" t="inlineStr">
         <is>
           <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
-      <c r="E66" s="24" t="inlineStr">
+      <c r="E66" s="25" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -25741,27 +25741,27 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="25" t="inlineStr">
         <is>
           <t>Neumático macizo — Ø300 × 55 de ancho</t>
         </is>
       </c>
-      <c r="B67" s="24" t="inlineStr">
+      <c r="B67" s="25" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
+      <c r="C67" s="25" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D67" s="24" t="inlineStr">
+      <c r="D67" s="25" t="inlineStr">
         <is>
           <t>Ruedar</t>
         </is>
       </c>
-      <c r="E67" s="24" t="inlineStr">
+      <c r="E67" s="25" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -25884,27 +25884,27 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="25" t="inlineStr">
+      <c r="A69" s="23" t="inlineStr">
         <is>
           <t>Neumático macizo — Ø400 × 80 de ancho</t>
         </is>
       </c>
-      <c r="B69" s="25" t="inlineStr">
+      <c r="B69" s="23" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C69" s="25" t="inlineStr">
+      <c r="C69" s="23" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D69" s="25" t="inlineStr">
+      <c r="D69" s="23" t="inlineStr">
         <is>
           <t>Ruedar</t>
         </is>
       </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="E69" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -26915,27 +26915,27 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="23" t="inlineStr">
+      <c r="A83" s="24" t="inlineStr">
         <is>
           <t>Alambre MAG ER70S-6 Ø0,9 (AWS A5.18)</t>
         </is>
       </c>
-      <c r="B83" s="23" t="inlineStr">
+      <c r="B83" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C83" s="23" t="inlineStr">
+      <c r="C83" s="24" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D83" s="23" t="inlineStr">
+      <c r="D83" s="24" t="inlineStr">
         <is>
           <t>Conarco (ESAB Argentina)</t>
         </is>
       </c>
-      <c r="E83" s="23" t="inlineStr">
+      <c r="E83" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -26994,27 +26994,27 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="23" t="inlineStr">
+      <c r="A84" s="24" t="inlineStr">
         <is>
           <t>Alambre MAG ER70S-6 Ø1,2 (AWS A5.18)</t>
         </is>
       </c>
-      <c r="B84" s="23" t="inlineStr">
+      <c r="B84" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C84" s="23" t="inlineStr">
+      <c r="C84" s="24" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D84" s="23" t="inlineStr">
+      <c r="D84" s="24" t="inlineStr">
         <is>
           <t>Conarco (ESAB Argentina)</t>
         </is>
       </c>
-      <c r="E84" s="23" t="inlineStr">
+      <c r="E84" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -27060,40 +27060,40 @@
         <v/>
       </c>
       <c r="AO84" s="22" t="n">
-        <v>0.3374</v>
+        <v>0.3429</v>
       </c>
       <c r="AP84" s="22" t="n">
-        <v>0.4194</v>
+        <v>0.426</v>
       </c>
       <c r="AQ84" s="22" t="n">
-        <v>0.9806</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="AR84" s="22" t="n">
-        <v>1.0848</v>
+        <v>1.0968</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="23" t="inlineStr">
+      <c r="A85" s="24" t="inlineStr">
         <is>
           <t>Gas de protección MAG Arcal 21 / ARCAL Speed (Ar + 8 % CO₂, M20)</t>
         </is>
       </c>
-      <c r="B85" s="23" t="inlineStr">
+      <c r="B85" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C85" s="23" t="inlineStr">
+      <c r="C85" s="24" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D85" s="23" t="inlineStr">
+      <c r="D85" s="24" t="inlineStr">
         <is>
           <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
-      <c r="E85" s="23" t="inlineStr">
+      <c r="E85" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -27151,40 +27151,40 @@
         <v>40.7</v>
       </c>
       <c r="AO85" s="22" t="n">
-        <v>52.7</v>
+        <v>54.8</v>
       </c>
       <c r="AP85" s="22" t="n">
-        <v>65.8</v>
+        <v>68.3</v>
       </c>
       <c r="AQ85" s="22" t="n">
-        <v>73.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AR85" s="22" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="25" t="inlineStr">
+      <c r="A86" s="23" t="inlineStr">
         <is>
           <t>Granalla de acero S330 / S390 (ISO 11124-3, SAE J444)</t>
         </is>
       </c>
-      <c r="B86" s="25" t="inlineStr">
+      <c r="B86" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C86" s="25" t="inlineStr">
+      <c r="C86" s="23" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D86" s="25" t="inlineStr">
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>CyM Materiales</t>
         </is>
       </c>
-      <c r="E86" s="25" t="inlineStr">
+      <c r="E86" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -27401,27 +27401,27 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="23" t="inlineStr">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>Gas impulsor: N₂</t>
         </is>
       </c>
-      <c r="B89" s="23" t="inlineStr">
+      <c r="B89" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C89" s="23" t="inlineStr">
+      <c r="C89" s="24" t="inlineStr">
         <is>
           <t>Carga (agente y gas)</t>
         </is>
       </c>
-      <c r="D89" s="23" t="inlineStr">
+      <c r="D89" s="24" t="inlineStr">
         <is>
           <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
-      <c r="E89" s="23" t="inlineStr">
+      <c r="E89" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -27492,27 +27492,27 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="23" t="inlineStr">
+      <c r="A90" s="24" t="inlineStr">
         <is>
           <t>Polvo químico seco ABC 60 (Sello IRAM 3569)</t>
         </is>
       </c>
-      <c r="B90" s="23" t="inlineStr">
+      <c r="B90" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C90" s="23" t="inlineStr">
+      <c r="C90" s="24" t="inlineStr">
         <is>
           <t>Carga (agente y gas)</t>
         </is>
       </c>
-      <c r="D90" s="23" t="inlineStr">
+      <c r="D90" s="24" t="inlineStr">
         <is>
           <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
-      <c r="E90" s="23" t="inlineStr">
+      <c r="E90" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -27571,27 +27571,27 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="23" t="inlineStr">
+      <c r="A91" s="24" t="inlineStr">
         <is>
           <t>Polvo químico seco ABC 90 (Sello IRAM 3569)</t>
         </is>
       </c>
-      <c r="B91" s="23" t="inlineStr">
+      <c r="B91" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C91" s="23" t="inlineStr">
+      <c r="C91" s="24" t="inlineStr">
         <is>
           <t>Carga (agente y gas)</t>
         </is>
       </c>
-      <c r="D91" s="23" t="inlineStr">
+      <c r="D91" s="24" t="inlineStr">
         <is>
           <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
-      <c r="E91" s="23" t="inlineStr">
+      <c r="E91" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -29255,27 +29255,27 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="23" t="inlineStr">
+      <c r="A113" s="24" t="inlineStr">
         <is>
           <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
         </is>
       </c>
-      <c r="B113" s="23" t="inlineStr">
+      <c r="B113" s="24" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="C113" s="23" t="inlineStr">
+      <c r="C113" s="24" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D113" s="23" t="inlineStr">
+      <c r="D113" s="24" t="inlineStr">
         <is>
           <t>MV Embalajes</t>
         </is>
       </c>
-      <c r="E113" s="23" t="inlineStr">
+      <c r="E113" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -29583,27 +29583,27 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="23" t="inlineStr">
+      <c r="A117" s="24" t="inlineStr">
         <is>
           <t>Film stretch (fracción del pallet)</t>
         </is>
       </c>
-      <c r="B117" s="23" t="inlineStr">
+      <c r="B117" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C117" s="23" t="inlineStr">
+      <c r="C117" s="24" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D117" s="23" t="inlineStr">
+      <c r="D117" s="24" t="inlineStr">
         <is>
           <t>MV Embalajes</t>
         </is>
       </c>
-      <c r="E117" s="23" t="inlineStr">
+      <c r="E117" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -30848,27 +30848,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CLASED_9l</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Equipo terminado comprado</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Matafuegos Georgia - venta mayorista</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -31921,27 +31921,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Chapa LAC 1500 × 3000 e=4,75</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Materia prima</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>Pradecon S.A.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -31987,10 +31987,10 @@
         <v/>
       </c>
       <c r="AQ19" s="22" t="n">
-        <v>41.925</v>
+        <v>55.953</v>
       </c>
       <c r="AR19" s="22" t="n">
-        <v>55.947</v>
+        <v>55.91</v>
       </c>
     </row>
     <row r="20">
@@ -32694,27 +32694,27 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>Redondo liso SAE 1010 Ø8</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>barra 6 m</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Materia prima</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>Hierros Parrotta</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -32760,10 +32760,10 @@
         <v/>
       </c>
       <c r="AQ30" s="22" t="n">
-        <v>0.1089</v>
+        <v>0.128</v>
       </c>
       <c r="AR30" s="22" t="n">
-        <v>0.1265</v>
+        <v>0.1478</v>
       </c>
     </row>
     <row r="31">
@@ -33753,27 +33753,27 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="24" t="inlineStr">
         <is>
           <t>Alambre MAG ER70S-6 Ø0,9 (AWS A5.18)</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="24" t="inlineStr">
         <is>
           <t>Conarco (ESAB Argentina)</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -33832,27 +33832,27 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="24" t="inlineStr">
         <is>
           <t>Alambre MAG ER70S-6 Ø1,2 (AWS A5.18)</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>Conarco (ESAB Argentina)</t>
         </is>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -33898,40 +33898,40 @@
         <v/>
       </c>
       <c r="AO46" s="22" t="n">
-        <v>0.3374</v>
+        <v>0.3429</v>
       </c>
       <c r="AP46" s="22" t="n">
-        <v>0.4194</v>
+        <v>0.426</v>
       </c>
       <c r="AQ46" s="22" t="n">
-        <v>0.9806</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="AR46" s="22" t="n">
-        <v>1.0848</v>
+        <v>1.0968</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>Gas de protección MAG Arcal 21 / ARCAL Speed (Ar + 8 % CO₂, M20)</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -33989,40 +33989,40 @@
         <v>40.7</v>
       </c>
       <c r="AO47" s="22" t="n">
-        <v>52.7</v>
+        <v>54.8</v>
       </c>
       <c r="AP47" s="22" t="n">
-        <v>65.8</v>
+        <v>68.3</v>
       </c>
       <c r="AQ47" s="22" t="n">
-        <v>73.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AR47" s="22" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="25" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>Granalla de acero S330 / S390 (ISO 11124-3, SAE J444)</t>
         </is>
       </c>
-      <c r="B48" s="25" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C48" s="25" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D48" s="25" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>CyM Materiales</t>
         </is>
       </c>
-      <c r="E48" s="25" t="inlineStr">
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -34610,27 +34610,27 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="24" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="24" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="24" t="inlineStr">
         <is>
           <t>MV Embalajes</t>
         </is>
       </c>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -34938,27 +34938,27 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="A60" s="24" t="inlineStr">
         <is>
           <t>Film stretch (fracción del pallet)</t>
         </is>
       </c>
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C60" s="23" t="inlineStr">
+      <c r="C60" s="24" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D60" s="23" t="inlineStr">
+      <c r="D60" s="24" t="inlineStr">
         <is>
           <t>MV Embalajes</t>
         </is>
       </c>
-      <c r="E60" s="23" t="inlineStr">
+      <c r="E60" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -35199,27 +35199,27 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="25" t="inlineStr">
+      <c r="A63" s="23" t="inlineStr">
         <is>
           <t>Tapón protector de rosca del cuello</t>
         </is>
       </c>
-      <c r="B63" s="25" t="inlineStr">
+      <c r="B63" s="23" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C63" s="25" t="inlineStr">
+      <c r="C63" s="23" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D63" s="25" t="inlineStr">
+      <c r="D63" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="E63" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -37944,27 +37944,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Gas impulsor: N₂</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Carga (agente y gas)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -38135,27 +38135,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Polvo químico seco ABC 60 (Sello IRAM 3569)</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Carga (agente y gas)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -38298,27 +38298,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Polvo químico seco ABC 90 (Sello IRAM 3569)</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Carga (agente y gas)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -38461,27 +38461,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Acetato de potasio - DEMSA Kitchen (IRAM 3697)</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>Recarga y mantenimiento</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -38612,27 +38612,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Concentrado espumígeno AFFF 3 % (IRAM 3515)</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>Recarga y mantenimiento</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -39443,27 +39443,27 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>HCFC 123 / HFC 236fa (agente limpio)</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>Recarga y mantenimiento</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -39594,27 +39594,27 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>Junta tórica de asiento del cuello</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Recarga y mantenimiento</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>Argensold</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -40239,27 +40239,27 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Polvo para metales combustibles clase D</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>Recarga y mantenimiento</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="25" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -40390,27 +40390,27 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Polvo químico seco BC (bicarbonato)</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>Recarga y mantenimiento</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>

--- a/salida/mrp/MRP_MP.xlsx
+++ b/salida/mrp/MRP_MP.xlsx
@@ -8813,7 +8813,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.219 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.043 de largo desarrollado</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.321 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.339 de largo desarrollado</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.664 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 671 de largo desarrollado</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 968 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 892 de largo desarrollado</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.053 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.045 de largo desarrollado</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 656 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 645 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 848 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 839 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 999 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 991 de largo desarrollado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -9684,7 +9684,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø300 × 49 de ancho</t>
+          <t>Neumático macizo — Ø300 × 60 de ancho</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø350 × 49 de ancho</t>
+          <t>Neumático macizo — Ø350 × 60 de ancho</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø400 × 76 de ancho</t>
+          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Ruedar</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -9885,7 +9885,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
+          <t>Racor de manguera — 24 × 24 × 16</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 24 × 24 × 16</t>
+          <t>Remito de préstamo con membrete (n° de extintor, puesto, equipo retirado, fechas) — A5 duplicado</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>u/préstamo</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -9967,64 +9967,64 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_SUSTITUTOS</t>
         </is>
       </c>
       <c r="F59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="G59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="H59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="I59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="J59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="K59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="L59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="M59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="N59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="O59" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Remito de préstamo con membrete (n° de extintor, puesto, equipo retirado, fechas) — A5 duplicado</t>
+          <t>Rueda con cubierta neumática — Ø400 × 100 de ancho</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>u/préstamo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -10034,52 +10034,52 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Escanort S.A.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MP_SUSTITUTOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="G60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="H60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="I60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="J60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="K60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="L60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="M60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="N60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="O60" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
         <v/>
       </c>
     </row>
@@ -21754,16 +21754,16 @@
         <v/>
       </c>
       <c r="AO17" s="22" t="n">
-        <v>0.2774</v>
+        <v>0.2797</v>
       </c>
       <c r="AP17" s="22" t="n">
-        <v>0.2767</v>
+        <v>0.2789</v>
       </c>
       <c r="AQ17" s="22" t="n">
-        <v>0.3162</v>
+        <v>0.3184</v>
       </c>
       <c r="AR17" s="22" t="n">
-        <v>0.2998</v>
+        <v>0.3021</v>
       </c>
     </row>
     <row r="18">
@@ -22749,16 +22749,16 @@
         <v/>
       </c>
       <c r="AO31" s="22" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AP31" s="22" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="AQ31" s="22" t="n">
-        <v>0.0958</v>
+        <v>0.095</v>
       </c>
       <c r="AR31" s="22" t="n">
-        <v>0.105</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="32">
@@ -23920,7 +23920,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.219 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.043 de largo desarrollado</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -23983,14 +23983,14 @@
         <f>SUMPRODUCT($AK48:$AR48,$AK$14:$AR$14)*IF($E48="CABA",'Parametros'!K$7,IF($E48="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP48" s="22" t="n">
+      <c r="AQ48" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.321 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.339 de largo desarrollado</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -24053,14 +24053,14 @@
         <f>SUMPRODUCT($AK49:$AR49,$AK$14:$AR$14)*IF($E49="CABA",'Parametros'!K$7,IF($E49="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ49" s="22" t="n">
+      <c r="AR49" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.664 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 671 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -24123,14 +24123,14 @@
         <f>SUMPRODUCT($AK50:$AR50,$AK$14:$AR$14)*IF($E50="CABA",'Parametros'!K$7,IF($E50="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR50" s="22" t="n">
+      <c r="AO50" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 968 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 892 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -24193,14 +24193,14 @@
         <f>SUMPRODUCT($AK51:$AR51,$AK$14:$AR$14)*IF($E51="CABA",'Parametros'!K$7,IF($E51="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO51" s="22" t="n">
+      <c r="AP51" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.053 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.045 de largo desarrollado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -24480,7 +24480,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 656 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 645 de largo desarrollado</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -24550,7 +24550,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 848 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 839 de largo desarrollado</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -24620,7 +24620,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 999 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 991 de largo desarrollado</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -24848,7 +24848,7 @@
     <row r="61">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø300 × 49 de ancho</t>
+          <t>Neumático macizo — Ø300 × 60 de ancho</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
@@ -24918,7 +24918,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø350 × 49 de ancho</t>
+          <t>Neumático macizo — Ø350 × 60 de ancho</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -24989,27 +24989,27 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="25" t="inlineStr">
-        <is>
-          <t>Neumático macizo — Ø400 × 76 de ancho</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C63" s="25" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D63" s="25" t="inlineStr">
-        <is>
-          <t>Ruedar</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -25054,14 +25054,20 @@
         <f>SUMPRODUCT($AK63:$AR63,$AK$14:$AR$14)*IF($E63="CABA",'Parametros'!K$7,IF($E63="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR63" s="22" t="n">
-        <v>2</v>
+      <c r="AL63" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM63" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN63" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
+          <t>Racor de manguera — 24 × 24 × 16</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -25124,20 +25130,23 @@
         <f>SUMPRODUCT($AK64:$AR64,$AK$14:$AR$14)*IF($E64="CABA",'Parametros'!K$7,IF($E64="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL64" s="22" t="n">
+      <c r="AO64" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AM64" s="22" t="n">
+      <c r="AP64" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AN64" s="22" t="n">
+      <c r="AQ64" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR64" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 24 × 24 × 16</t>
+          <t>Rueda con cubierta neumática — Ø400 × 100 de ancho</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -25152,7 +25161,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Escanort S.A.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -25200,17 +25209,8 @@
         <f>SUMPRODUCT($AK65:$AR65,$AK$14:$AR$14)*IF($E65="CABA",'Parametros'!K$7,IF($E65="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO65" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP65" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ65" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AR65" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">

--- a/salida/mrp/MRP_MP.xlsx
+++ b/salida/mrp/MRP_MP.xlsx
@@ -9215,7 +9215,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 328 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 517 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 645 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 647 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -12766,7 +12766,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 261 × 214 × 628 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado doble — 258 × 214 × 628 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -12967,7 +12967,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 163 × 107 × 348 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -13101,7 +13101,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 232 × 157 × 379 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 229 × 157 × 379 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -13168,7 +13168,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 247 × 186 × 455 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 244 × 186 × 455 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 328 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -24410,7 +24410,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 517 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -24480,7 +24480,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 645 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 647 de largo desarrollado</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -28015,7 +28015,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 261 × 214 × 628 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado doble — 258 × 214 × 628 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -28085,7 +28085,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 163 × 107 × 348 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -28155,7 +28155,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 232 × 157 × 379 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 229 × 157 × 379 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -28225,7 +28225,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 247 × 186 × 455 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 244 × 186 × 455 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -28359,16 +28359,16 @@
         <v/>
       </c>
       <c r="AK106" s="22" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="AL106" s="22" t="n">
-        <v>0.744</v>
+        <v>0.738</v>
       </c>
       <c r="AM106" s="22" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="AN106" s="22" t="n">
-        <v>0.802</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="107">

--- a/salida/mrp/MRP_MP.xlsx
+++ b/salida/mrp/MRP_MP.xlsx
@@ -8813,7 +8813,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.043 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.037 de largo desarrollado</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.339 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.305 de largo desarrollado</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 671 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.371 de largo desarrollado</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 892 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.714 de largo desarrollado</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.045 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 647 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 839 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 991 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Alambre MAG ER70S-6 Ø1,2 (AWS A5.18)</t>
+          <t>Alambre MAG ER70S-6 Ø1,0 (AWS A5.18)</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 168 × 136 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 168 × 137 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11694,7 +11694,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 234 × 151 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 234 × 152 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 289 × 142 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 289 × 144 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11828,7 +11828,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 343 × 221 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 343 × 224 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 522 × 208 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 522 × 210 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 604 × 204 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 604 × 207 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -12029,7 +12029,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 736 × 211 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 736 × 214 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -21754,16 +21754,16 @@
         <v/>
       </c>
       <c r="AO17" s="22" t="n">
-        <v>0.2797</v>
+        <v>0.2216</v>
       </c>
       <c r="AP17" s="22" t="n">
-        <v>0.2789</v>
+        <v>0.219</v>
       </c>
       <c r="AQ17" s="22" t="n">
-        <v>0.3184</v>
+        <v>0.2566</v>
       </c>
       <c r="AR17" s="22" t="n">
-        <v>0.3021</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="18">
@@ -23920,7 +23920,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.043 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.037 de largo desarrollado</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -23983,14 +23983,14 @@
         <f>SUMPRODUCT($AK48:$AR48,$AK$14:$AR$14)*IF($E48="CABA",'Parametros'!K$7,IF($E48="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ48" s="22" t="n">
+      <c r="AO48" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.339 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.305 de largo desarrollado</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -24053,14 +24053,14 @@
         <f>SUMPRODUCT($AK49:$AR49,$AK$14:$AR$14)*IF($E49="CABA",'Parametros'!K$7,IF($E49="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR49" s="22" t="n">
+      <c r="AP49" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 671 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.371 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -24123,14 +24123,14 @@
         <f>SUMPRODUCT($AK50:$AR50,$AK$14:$AR$14)*IF($E50="CABA",'Parametros'!K$7,IF($E50="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO50" s="22" t="n">
+      <c r="AQ50" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 892 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.714 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -24193,14 +24193,14 @@
         <f>SUMPRODUCT($AK51:$AR51,$AK$14:$AR$14)*IF($E51="CABA",'Parametros'!K$7,IF($E51="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP51" s="22" t="n">
+      <c r="AR51" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.045 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -24263,14 +24263,14 @@
         <f>SUMPRODUCT($AK52:$AR52,$AK$14:$AR$14)*IF($E52="CABA",'Parametros'!K$7,IF($E52="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR52" s="22" t="n">
+      <c r="AO52" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -24333,14 +24333,14 @@
         <f>SUMPRODUCT($AK53:$AR53,$AK$14:$AR$14)*IF($E53="CABA",'Parametros'!K$7,IF($E53="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL53" s="22" t="n">
+      <c r="AP53" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -24403,14 +24403,14 @@
         <f>SUMPRODUCT($AK54:$AR54,$AK$14:$AR$14)*IF($E54="CABA",'Parametros'!K$7,IF($E54="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM54" s="22" t="n">
+      <c r="AQ54" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -24473,14 +24473,14 @@
         <f>SUMPRODUCT($AK55:$AR55,$AK$14:$AR$14)*IF($E55="CABA",'Parametros'!K$7,IF($E55="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN55" s="22" t="n">
+      <c r="AR55" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 647 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -24543,14 +24543,14 @@
         <f>SUMPRODUCT($AK56:$AR56,$AK$14:$AR$14)*IF($E56="CABA",'Parametros'!K$7,IF($E56="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO56" s="22" t="n">
+      <c r="AL56" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 839 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -24613,14 +24613,14 @@
         <f>SUMPRODUCT($AK57:$AR57,$AK$14:$AR$14)*IF($E57="CABA",'Parametros'!K$7,IF($E57="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP57" s="22" t="n">
+      <c r="AM57" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 991 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -24683,7 +24683,7 @@
         <f>SUMPRODUCT($AK58:$AR58,$AK$14:$AR$14)*IF($E58="CABA",'Parametros'!K$7,IF($E58="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ58" s="22" t="n">
+      <c r="AN58" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26101,7 +26101,7 @@
     <row r="78">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>Alambre MAG ER70S-6 Ø1,2 (AWS A5.18)</t>
+          <t>Alambre MAG ER70S-6 Ø1,0 (AWS A5.18)</t>
         </is>
       </c>
       <c r="B78" s="23" t="inlineStr">
@@ -26848,7 +26848,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 168 × 136 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 168 × 137 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -26918,7 +26918,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 234 × 151 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 234 × 152 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -26988,7 +26988,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 289 × 142 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 289 × 144 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -27058,7 +27058,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 343 × 221 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 343 × 224 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -27128,7 +27128,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 522 × 208 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 522 × 210 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -27198,7 +27198,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 604 × 204 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 604 × 207 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 736 × 211 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 736 × 214 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -32665,7 +32665,7 @@
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>Alambre MAG ER70S-6 Ø1,2 (AWS A5.18)</t>
+          <t>Alambre MAG ER70S-6 Ø1,0 (AWS A5.18)</t>
         </is>
       </c>
       <c r="B43" s="23" t="inlineStr">

--- a/salida/mrp/MRP_MP.xlsx
+++ b/salida/mrp/MRP_MP.xlsx
@@ -20,12 +20,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MRP_CONSOLIDADO" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MP_MATAFUEGOS_FABRICADOS'!$A$16:$E$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MP_MATAFUEGOS_FABRICADOS'!$A$16:$E$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'MP_MATAFUEGOS_REVENDIDOS'!$A$16:$E$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'MP_CILINDROS'!$A$16:$E$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MP_SUSTITUTOS'!$A$16:$E$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'MP_RECARGAS'!$A$16:$E$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MRP_CONSOLIDADO'!$A$4:$E$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MRP_CONSOLIDADO'!$A$4:$E$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6240,7 +6240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O140"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -6401,7 +6401,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Caño Ø76,2 × 1,25</t>
+          <t>Caño SAE 1010 Ø33,7 × 3,25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -6421,59 +6421,59 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="G6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="H6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="I6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="J6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="K6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="L6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="M6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="N6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
       <c r="O6" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A6,'MP_CILINDROS'!$B:$B,$B6)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A6,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAC 1500 × 3000 e=3,2</t>
+          <t>Caño Ø76,2 × 1,25</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>barra 6 m</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Pradecon S.A.</t>
+          <t>Metalpri / Prilux</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAC 1500 × 3000 e=4,75</t>
+          <t>Chapa LAC 1500 × 3000 e=3,2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -6602,7 +6602,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAF 1000 × 2000 e=1,6</t>
+          <t>Chapa LAC 1500 × 3000 e=4,75</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAF 1220 × 2440 e=1,25</t>
+          <t>Chapa LAF 1000 × 2000 e=1,6</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAF 1500 × 3000 e=2</t>
+          <t>Chapa LAF 1220 × 2440 e=1,25</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=0,9 × 114</t>
+          <t>Chapa LAF 1500 × 3000 e=2</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Pacheco Chapas</t>
+          <t>Pradecon S.A.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6870,7 +6870,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,25 × 106</t>
+          <t>Fleje e=0,9 × 114</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,25 × 200</t>
+          <t>Fleje e=1,25 × 106</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,6 × 200</t>
+          <t>Fleje e=1,25 × 200</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,6 × 250</t>
+          <t>Fleje e=1,6 × 200</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,6 × 300</t>
+          <t>Fleje e=1,6 × 250</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=2 × 249</t>
+          <t>Fleje e=1,6 × 300</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Redondo SAE 1045 Ø25</t>
+          <t>Fleje e=2 × 249</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>barra 6 m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7287,126 +7287,126 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Hierros Parrotta</t>
+          <t>Pacheco Chapas</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="G19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="H19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="I19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="J19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="K19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="L19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="M19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="N19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
       <c r="O19" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A19,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B19)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A19,'MP_CILINDROS'!$B:$B,$B19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø29 × 12,5 de alto, rosca M22x1,5, asiento Ø26</t>
+          <t>Redondo SAE 1045 Ø25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>barra 6 m</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Semielaborado comprado</t>
+          <t>Materia prima</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Eli-Met</t>
+          <t>Hierros Parrotta</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="G20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="H20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="I20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="J20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="K20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="L20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="M20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="N20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
       <c r="O20" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A20,'MP_CILINDROS'!$B:$B,$B20)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A20,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø36,8 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø29 × 12,5 de alto, rosca M22x1,5, asiento Ø26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø37 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø36,8 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø37 × 15 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø37 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -7607,7 +7607,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø37 × 35 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø37 × 15 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø88 × 37 de alto, rosca RBSP 2 1/2"-11 h, asiento Ø80</t>
+          <t>Cuello roscado — Ø37 × 35 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Cúpula — Ø276,5 × e3,2 × 94,4 de alto; disco Ø358,3</t>
+          <t>Cuello roscado — Ø88 × 37 de alto, rosca RBSP 2 1/2"-11 h, asiento Ø80</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Gockel Ingeniería S.R.L.</t>
+          <t>Eli-Met</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Cúpula — Ø320 × e3,2 × 109,9 de alto; disco Ø410,8</t>
+          <t>Cúpula — Ø276,5 × e3,2 × 94,4 de alto; disco Ø358,3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Cúpula — Ø390 × e4,75 × 137,3 de alto; disco Ø507,3</t>
+          <t>Cúpula — Ø320 × e3,2 × 109,9 de alto; disco Ø410,8</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Fondo — Ø276,5 × e3,2 × 95 de alto; disco Ø362,5</t>
+          <t>Cúpula — Ø390 × e4,75 × 137,3 de alto; disco Ø507,3</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Fondo — Ø320 × e3,2 × 113 de alto; disco Ø423,5</t>
+          <t>Fondo — Ø276,5 × e3,2 × 95 de alto; disco Ø362,5</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Fondo — Ø390 × e4,75 × 139,8 de alto; disco Ø518,1</t>
+          <t>Fondo — Ø320 × e3,2 × 113 de alto; disco Ø423,5</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -8143,7 +8143,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Arandelas de tope (4) — 4 × Ø40 × Ø26 × 4</t>
+          <t>Fondo — Ø390 × e4,75 × 139,8 de alto; disco Ø518,1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8153,64 +8153,64 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Componente comprado</t>
+          <t>Semielaborado comprado</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Hierros Parrotta</t>
+          <t>Gockel Ingeniería S.R.L.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="G32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="H32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="I32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="J32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="K32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="L32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="M32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="N32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
       <c r="O32" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A32,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B32)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A32,'MP_CILINDROS'!$B:$B,$B32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 1025 (alto ≤ 40; perímetro + 20 de solape)</t>
+          <t>Arandelas de tope (4) — 4 × Ø40 × Ø26 × 4</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -8225,59 +8225,59 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Hierros Parrotta</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MP_SUSTITUTOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="G33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="H33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="I33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="J33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="K33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="L33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="M33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="N33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
       <c r="O33" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A33,'MP_SUSTITUTOS'!$B:$B,$B33)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A33,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 1245 (alto ≤ 40; perímetro + 20 de solape)</t>
+          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 1025 (alto ≤ 40; perímetro + 20 de solape)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 460 (alto ≤ 40; perímetro + 20 de solape)</t>
+          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 1245 (alto ≤ 40; perímetro + 20 de solape)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 501 (alto ≤ 40; perímetro + 20 de solape)</t>
+          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 460 (alto ≤ 40; perímetro + 20 de solape)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 590 (alto ≤ 40; perímetro + 20 de solape)</t>
+          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 501 (alto ≤ 40; perímetro + 20 de solape)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 617 (alto ≤ 40; perímetro + 20 de solape)</t>
+          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 590 (alto ≤ 40; perímetro + 20 de solape)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento — Ø24 ext. × cordón 3</t>
+          <t>Faja amarilla de sustituto en la pollera (3 leyendas) — 40 × 617 (alto ≤ 40; perímetro + 20 de solape)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -8627,59 +8627,59 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Argensold</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_SUSTITUTOS</t>
         </is>
       </c>
       <c r="F39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="G39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="H39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="I39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="J39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="K39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="L39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="M39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="N39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
       <c r="O39" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A39,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B39)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A39,'MP_SUSTITUTOS'!$B:$B,$B39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento — Ø32,8 ext. × cordón 3</t>
+          <t>Junta tórica de asiento — Ø24 ext. × cordón 3</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8746,7 +8746,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento — Ø78 ext. × cordón 3</t>
+          <t>Junta tórica de asiento — Ø32,8 ext. × cordón 3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.037 de largo desarrollado</t>
+          <t>Junta tórica de asiento — Ø78 ext. × cordón 3</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Argensold</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.305 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.037 de largo desarrollado</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.371 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.305 de largo desarrollado</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.714 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.371 de largo desarrollado</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.714 de largo desarrollado</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -9550,7 +9550,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Manómetro — Ø36 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
+          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Manómetro — Ø47 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
+          <t>Manómetro — Ø36 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -9684,7 +9684,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø300 × 60 de ancho</t>
+          <t>Manómetro — Ø47 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Ruedar</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø350 × 60 de ancho</t>
+          <t>Neumático macizo — Ø300 × 60 de ancho</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
+          <t>Neumático macizo — Ø350 × 60 de ancho</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Ruedar</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -9885,7 +9885,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 24 × 24 × 16</t>
+          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Remito de préstamo con membrete (n° de extintor, puesto, equipo retirado, fechas) — A5 duplicado</t>
+          <t>Racor de manguera — 24 × 24 × 16</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>u/préstamo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -9967,64 +9967,64 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MP_SUSTITUTOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="G59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="H59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="I59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="J59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="K59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="L59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="M59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="N59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
       <c r="O59" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A59,'MP_SUSTITUTOS'!$B:$B,$B59)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A59,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Rueda con cubierta neumática — Ø400 × 100 de ancho</t>
+          <t>Remito de préstamo con membrete (n° de extintor, puesto, equipo retirado, fechas) — A5 duplicado</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>u/préstamo</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -10034,59 +10034,59 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Escanort S.A.</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_SUSTITUTOS</t>
         </is>
       </c>
       <c r="F60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="G60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="H60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="I60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="J60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="K60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="L60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="M60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="N60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
       <c r="O60" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A60,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B60)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A60,'MP_SUSTITUTOS'!$B:$B,$B60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Suncho portatobera — 137,3 × 127 × 14,4</t>
+          <t>Rueda con cubierta neumática — Ø400 × 100 de ancho</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Escanort S.A.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Suncho portatobera — 166,3 × 156 × 14,4</t>
+          <t>Suncho portatobera — 137,6 × 127,6 × 14,4</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Suncho portatobera — 194,8 × 184,5 × 14,4</t>
+          <t>Suncho portatobera — 166,6 × 156,6 × 14,4</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -10287,7 +10287,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta AGC con «Es sustituto» (sin domicilio de instalación) — formato oficial</t>
+          <t>Suncho portatobera — 195,1 × 185,1 × 14,4</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -10302,59 +10302,59 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Agencia Gubernamental de Control (CABA)</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MP_SUSTITUTOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="G64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="H64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="I64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="J64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="K64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="L64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="M64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="N64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
       <c r="O64" s="21">
-        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A64,'MP_SUSTITUTOS'!$B:$B,$B64)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A64,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación DPS con sello «SUSTITUTO HABILITADO» — formato oficial</t>
+          <t>Tarjeta AGC con «Es sustituto» (sin domicilio de instalación) — formato oficial</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Agencia Gubernamental de Control (CABA)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Tobera campana — 200 × 68 × 68</t>
+          <t>Tarjeta de identificación DPS con sello «SUSTITUTO HABILITADO» — formato oficial</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -10436,59 +10436,59 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_SUSTITUTOS</t>
         </is>
       </c>
       <c r="F66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!F:F,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="G66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!G:G,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="H66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!H:H,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="I66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!I:I,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="J66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!J:J,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="K66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!K:K,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="L66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!L:L,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="M66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!M:M,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="N66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!N:N,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
       <c r="O66" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A66,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B66)</f>
+        <f>SUMIFS('MP_SUSTITUTOS'!O:O,'MP_SUSTITUTOS'!$A:$A,$A66,'MP_SUSTITUTOS'!$B:$B,$B66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Tobera con portatobera — 73,5 × 19,9 × 19,9</t>
+          <t>Tobera campana — 200 × 68 × 68</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Tobera — 12 × 12 × 10</t>
+          <t>Tobera con portatobera — 73,5 × 19,9 × 19,9</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada M-22 1 kg c/tubo de pesca plástico</t>
+          <t>Tobera — 12 × 12 × 10</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -10689,7 +10689,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada M-30 c/resorte y tubo 7/8</t>
+          <t>Válvula HZ armada M-22 1 kg c/tubo de pesca plástico</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada de carro 25 kg c/traba, manija y resorte</t>
+          <t>Válvula HZ armada M-30 c/resorte y tubo 7/8</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada de carro 50-70-100 kg</t>
+          <t>Válvula HZ armada de carro 25 kg c/traba, manija y resorte</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Válvula esférica — 110 × 60 × 40</t>
+          <t>Válvula HZ armada de carro 50-70-100 kg</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -10957,74 +10957,74 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Alambre MAG ER70S-6 Ø0,9 (AWS A5.18)</t>
+          <t>Válvula esférica — 110 × 60 × 40</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Consumible de proceso</t>
+          <t>Componente comprado</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Conarco (ESAB Argentina)</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="G74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="H74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="I74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="J74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="K74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="L74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="M74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="N74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
       <c r="O74" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A74,'MP_CILINDROS'!$B:$B,$B74)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A74,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B74)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Alambre MAG ER70S-6 Ø1,0 (AWS A5.18)</t>
+          <t>Alambre MAG ER70S-6 Ø0,9 (AWS A5.18)</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Gas de protección MAG Arcal 21 / ARCAL Speed (Ar + 8 % CO₂, M20)</t>
+          <t>Alambre MAG ER70S-6 Ø1,0 (AWS A5.18)</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+          <t>Conarco (ESAB Argentina)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Granalla de acero S330 / S390 (ISO 11124-3, SAE J444)</t>
+          <t>Gas de protección MAG Arcal 21 / ARCAL Speed (Ar + 8 % CO₂, M20)</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>CyM Materiales</t>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -11225,22 +11225,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Servicio de pintura en polvo al horno, rojo 03-1-050</t>
+          <t>Granalla de acero S330 / S390 (ISO 11124-3, SAE J444)</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Servicio</t>
+          <t>Consumible de proceso</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Prymax</t>
+          <t>CyM Materiales</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Servicio de pintura en polvo al horno, rojo 03-1-050 (con preparación por quemado)</t>
+          <t>Servicio de pintura en polvo al horno, rojo 03-1-050</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Pintor de carros (cotización por mensaje)</t>
+          <t>Prymax</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -11359,74 +11359,74 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Gas impulsor: N₂</t>
+          <t>Servicio de pintura en polvo al horno, rojo 03-1-050 (con preparación por quemado)</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Carga (agente y gas)</t>
+          <t>Servicio</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+          <t>Pintor de carros (cotización por mensaje)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_RECARGAS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="G80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="H80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="I80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="J80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="K80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="L80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="M80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="N80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
       <c r="O80" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A80,'MP_RECARGAS'!$B:$B,$B80)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A80,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B80)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A80,'MP_CILINDROS'!$B:$B,$B80)</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Polvo químico seco ABC 60 (Sello IRAM 3569)</t>
+          <t>Gas impulsor: N₂</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>DEM S.A. (DEMSA)</t>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -11493,7 +11493,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Polvo químico seco ABC 90 (Sello IRAM 3569)</t>
+          <t>Polvo químico seco ABC 60 (Sello IRAM 3569)</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -11560,74 +11560,74 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Estampilla IRAM de conformidad — 60 × 40</t>
+          <t>Polvo químico seco ABC 90 (Sello IRAM 3569)</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Identificación</t>
+          <t>Carga (agente y gas)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>IRAM - Instituto Argentino de Normalización</t>
+          <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_RECARGAS</t>
         </is>
       </c>
       <c r="F83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="G83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="H83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="I83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="J83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="K83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="L83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="M83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="N83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
       <c r="O83" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A83,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B83)+SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A83,'MP_RECARGAS'!$B:$B,$B83)</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 168 × 137 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Estampilla IRAM de conformidad — 60 × 40</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>IRAM - Instituto Argentino de Normalización</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -11694,7 +11694,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 234 × 152 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 168 × 137 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 289 × 144 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 234 × 152 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -11828,7 +11828,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 343 × 224 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 289 × 144 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 522 × 210 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 343 × 224 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 604 × 207 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 522 × 210 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -12029,7 +12029,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 736 × 214 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 604 × 207 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -12096,7 +12096,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de identificación del cilindro suelto</t>
+          <t>Etiqueta / placa de características — 736 × 214 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -12116,54 +12116,54 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="G91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="H91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="I91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="J91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="K91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="L91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="M91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="N91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
       <c r="O91" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A91,'MP_CILINDROS'!$B:$B,$B91)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A91,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B91)</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de n° de serie GS1 — 45 × 25</t>
+          <t>Etiqueta de identificación del cilindro suelto</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -12183,54 +12183,54 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="G92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="H92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="I92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="J92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="K92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="L92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="M92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="N92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
       <c r="O92" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A92,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B92)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A92,'MP_CILINDROS'!$B:$B,$B92)</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Faja de garantía válvula-cuello — 30 × 40</t>
+          <t>Etiqueta de n° de serie GS1 — 45 × 25</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
+          <t>Faja de garantía válvula-cuello — 30 × 40</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -12364,7 +12364,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
+          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>SonFuertes (vía Papelera Damián)</t>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
+          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -12446,59 +12446,59 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Agencia Gubernamental de Control (CABA)</t>
+          <t>SonFuertes (vía Papelera Damián)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_MATAFUEGOS_REVENDIDOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="G96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="H96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="I96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="J96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="K96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="L96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="M96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="N96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
       <c r="O96" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A96,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B96)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A96,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B96)</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Soporte de pared (FL_ACC_01)</t>
+          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -12508,64 +12508,64 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Maxiseguridad</t>
+          <t>Agencia Gubernamental de Control (CABA)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_MATAFUEGOS_REVENDIDOS</t>
         </is>
       </c>
       <c r="F97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="G97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="H97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="I97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="J97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="K97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="L97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="M97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="N97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="O97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
+          <t>Soporte de pared (FL_ACC_01)</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Tornillo y tarugo de fijación</t>
+          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Würth Argentina</t>
+          <t>Maxiseguridad</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -12699,7 +12699,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 212 × 212 × 582 interior (envolvente del plano + 15 por lado)</t>
+          <t>Tornillo y tarugo de fijación</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12709,64 +12709,64 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Würth Argentina</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="G100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="H100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="I100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="J100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="K100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="L100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="M100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="N100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
       <c r="O100" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A100,'MP_CILINDROS'!$B:$B,$B100)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A100,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B100)</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 258 × 214 × 628 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado doble — 212 × 212 × 582 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -12786,54 +12786,54 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="G101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="H101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="I101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="J101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="K101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="L101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="M101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="N101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="O101" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 106 × 106 × 318 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado doble — 258 × 215 × 628 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -12853,54 +12853,54 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="G102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="H102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="I102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="J102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="K102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="L102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="M102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="N102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
       <c r="O102" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A102,'MP_CILINDROS'!$B:$B,$B102)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A102,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B102)</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 154 × 154 × 334 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 106 × 106 × 318 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -12967,7 +12967,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 154 × 154 × 334 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -12987,54 +12987,54 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="G104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="H104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="I104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="J104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="K104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="L104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="M104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="N104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="O104" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 183 × 183 × 410 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -13054,54 +13054,54 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="G105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="H105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="I105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="J105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="K105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="L105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="M105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="N105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="O105" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 229 × 157 × 379 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 183 × 183 × 410 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -13121,54 +13121,54 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="G106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="H106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="I106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="J106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="K106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="L106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="M106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="N106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="O106" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 244 × 186 × 455 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 229 × 158 × 379 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -13235,12 +13235,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
+          <t>Caja de cartón corrugado simple — 244 × 187 × 455 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -13250,64 +13250,64 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>MV Embalajes</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="G108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="H108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="I108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="J108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="K108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="L108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="M108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="N108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="O108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
+          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>MV Embalajes</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -13369,12 +13369,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
+          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>jgo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>MV Embalajes</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -13436,12 +13436,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de pallet (lote y destino, fracción)</t>
+          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>jgo</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>MV Embalajes</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -13503,12 +13503,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Film stretch (fracción del pallet)</t>
+          <t>Etiqueta de pallet (lote y destino, fracción)</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>MV Embalajes</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Instructivo de uso y mantenimiento</t>
+          <t>Film stretch (fracción del pallet)</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -13585,59 +13585,59 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>MV Embalajes</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="G113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="H113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="I113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="J113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="K113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="L113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="M113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="N113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
       <c r="O113" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A113,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B113)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A113,'MP_CILINDROS'!$B:$B,$B113)</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Pallet 1200 × 1000 (fracción)</t>
+          <t>Instructivo de uso y mantenimiento</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -13652,59 +13652,59 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>IndusPallets</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="G114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="H114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="I114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="J114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="K114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="L114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="M114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="N114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="O114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Separador de capa de cartón 1200 × 1000 (fracción del pallet)</t>
+          <t>Pallet 1200 × 1000 (fracción)</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -13719,59 +13719,59 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>IndusPallets</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="G115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="H115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="I115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="J115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="K115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="L115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="M115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="N115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
       <c r="O115" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A115,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B115)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A115,'MP_CILINDROS'!$B:$B,$B115)</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Tapón protector de rosca del cuello</t>
+          <t>Separador de capa de cartón 1200 × 1000 (fracción del pallet)</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_10l</t>
+          <t>Tapón protector de rosca del cuello</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -13848,64 +13848,64 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado</t>
+          <t>Embalaje</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Matafuegos Georgia - venta mayorista</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_REVENDIDOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="G117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="H117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="I117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="J117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="K117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="L117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="M117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="N117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="O117" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A117,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_50l</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_10l</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -13972,7 +13972,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AGUA_10l</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_50l</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_BC_5kg</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AGUA_10l</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -14106,7 +14106,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CLASED_9l</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_BC_5kg</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -14173,7 +14173,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_2kg</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CLASED_9l</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Mozart S.R.L.</t>
+          <t>Matafuegos Georgia - venta mayorista</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -14240,7 +14240,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_5kg</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_2kg</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -14307,7 +14307,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_HCFC-HFC_5kg</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_5kg</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Matafuegos Georgia - venta mayorista</t>
+          <t>Mozart S.R.L.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_SALESK_6l</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_HCFC-HFC_5kg</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -14441,74 +14441,74 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Acetato de potasio - DEMSA Kitchen (IRAM 3697)</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_SALESK_6l</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Recarga y mantenimiento</t>
+          <t>Equipo terminado comprado</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>Matafuegos Georgia - venta mayorista</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>MP_RECARGAS</t>
+          <t>MP_MATAFUEGOS_REVENDIDOS</t>
         </is>
       </c>
       <c r="F126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="G126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="H126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="I126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="J126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="K126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="L126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="M126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="N126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
       <c r="O126" s="21">
-        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A126,'MP_RECARGAS'!$B:$B,$B126)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A126,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B126)</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Concentrado espumígeno AFFF 3 % (IRAM 3515)</t>
+          <t>Acetato de potasio - DEMSA Kitchen (IRAM 3697)</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>DEM S.A. (DEMSA)</t>
+          <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -14575,12 +14575,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Disco de seguridad</t>
+          <t>Concentrado espumígeno AFFF 3 % (IRAM 3515)</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -14642,12 +14642,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Dióxido de carbono (IRAM 41170)</t>
+          <t>Disco de seguridad</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+          <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -14709,12 +14709,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de servicio del recargador (extintor n°, serie, próxima recarga y PH)</t>
+          <t>Dióxido de carbono (IRAM 41170)</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Gas impulsor: Argón</t>
+          <t>Etiqueta de servicio del recargador (extintor n°, serie, próxima recarga y PH)</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -14843,7 +14843,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>HCFC 123 / HFC 236fa (agente limpio)</t>
+          <t>Gas impulsor: Argón</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento del cuello</t>
+          <t>HCFC 123 / HFC 236fa (agente limpio)</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Argensold</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -14977,7 +14977,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Marbete (anillo, color del año)</t>
+          <t>Junta tórica de asiento del cuello</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Argensold</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -15044,7 +15044,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Oblea PBA de recarga Ø46 + estampilla precinto 1" × 200 mm válvula-cuerpo</t>
+          <t>Marbete (anillo, color del año)</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -15111,12 +15111,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Polvo para metales combustibles clase D</t>
+          <t>Oblea PBA de recarga Ø46 + estampilla precinto 1" × 200 mm válvula-cuerpo</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>DEM S.A. (DEMSA)</t>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -15178,7 +15178,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Polvo químico seco BC (bicarbonato)</t>
+          <t>Polvo para metales combustibles clase D</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -15245,12 +15245,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Precinto plástico numerado, color, con nombre del recargador</t>
+          <t>Polvo químico seco BC (bicarbonato)</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>SonFuertes (vía Papelera Damián)</t>
+          <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación AGC (módulo papel con QR + etiqueta AGC)</t>
+          <t>Precinto plástico numerado, color, con nombre del recargador</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Agencia Gubernamental de Control (CABA)</t>
+          <t>SonFuertes (vía Papelera Damián)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -15379,7 +15379,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación DPS de revisión / recarga</t>
+          <t>Tarjeta de identificación AGC (módulo papel con QR + etiqueta AGC)</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Agencia Gubernamental de Control (CABA)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -15443,8 +15443,75 @@
         <v/>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de identificación DPS de revisión / recarga</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Recarga y mantenimiento</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>MP_RECARGAS</t>
+        </is>
+      </c>
+      <c r="F141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="G141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="H141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="I141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="J141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="K141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="L141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="M141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="N141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+      <c r="O141" s="21">
+        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A141,'MP_RECARGAS'!$B:$B,$B141)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E140"/>
+  <autoFilter ref="A4:E141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21119,7 +21186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR112"/>
+  <dimension ref="A1:AR113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -21754,22 +21821,22 @@
         <v/>
       </c>
       <c r="AO17" s="22" t="n">
-        <v>0.2216</v>
+        <v>0.2666</v>
       </c>
       <c r="AP17" s="22" t="n">
-        <v>0.219</v>
+        <v>0.2615</v>
       </c>
       <c r="AQ17" s="22" t="n">
-        <v>0.2566</v>
+        <v>0.3071</v>
       </c>
       <c r="AR17" s="22" t="n">
-        <v>0.2366</v>
+        <v>0.2784</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Caño Ø76,2 × 1,25</t>
+          <t>Caño SAE 1010 Ø33,7 × 3,25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -21832,19 +21899,28 @@
         <f>SUMPRODUCT($AK18:$AR18,$AK$14:$AR$14)*IF($E18="CABA",'Parametros'!K$7,IF($E18="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK18" s="22" t="n">
-        <v>0.0435</v>
+      <c r="AO18" s="22" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AP18" s="22" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="AQ18" s="22" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AR18" s="22" t="n">
+        <v>0.067</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAC 1500 × 3000 e=3,2</t>
+          <t>Caño Ø76,2 × 1,25</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>barra 6 m</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -21854,7 +21930,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pradecon S.A.</t>
+          <t>Metalpri / Prilux</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -21902,17 +21978,14 @@
         <f>SUMPRODUCT($AK19:$AR19,$AK$14:$AR$14)*IF($E19="CABA",'Parametros'!K$7,IF($E19="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO19" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="AP19" s="22" t="n">
-        <v>18.845</v>
+      <c r="AK19" s="22" t="n">
+        <v>0.0435</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAC 1500 × 3000 e=4,75</t>
+          <t>Chapa LAC 1500 × 3000 e=3,2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -21975,17 +22048,17 @@
         <f>SUMPRODUCT($AK20:$AR20,$AK$14:$AR$14)*IF($E20="CABA",'Parametros'!K$7,IF($E20="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ20" s="22" t="n">
-        <v>38.802</v>
-      </c>
-      <c r="AR20" s="22" t="n">
-        <v>51.355</v>
+      <c r="AO20" s="22" t="n">
+        <v>12.558</v>
+      </c>
+      <c r="AP20" s="22" t="n">
+        <v>18.845</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAF 1000 × 2000 e=1,6</t>
+          <t>Chapa LAC 1500 × 3000 e=4,75</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -22048,14 +22121,17 @@
         <f>SUMPRODUCT($AK21:$AR21,$AK$14:$AR$14)*IF($E21="CABA",'Parametros'!K$7,IF($E21="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM21" s="22" t="n">
-        <v>2.092</v>
+      <c r="AQ21" s="22" t="n">
+        <v>38.802</v>
+      </c>
+      <c r="AR21" s="22" t="n">
+        <v>51.355</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAF 1220 × 2440 e=1,25</t>
+          <t>Chapa LAF 1000 × 2000 e=1,6</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -22118,14 +22194,14 @@
         <f>SUMPRODUCT($AK22:$AR22,$AK$14:$AR$14)*IF($E22="CABA",'Parametros'!K$7,IF($E22="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL22" s="22" t="n">
-        <v>1.082</v>
+      <c r="AM22" s="22" t="n">
+        <v>2.092</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Chapa LAF 1500 × 3000 e=2</t>
+          <t>Chapa LAF 1220 × 2440 e=1,25</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -22188,19 +22264,19 @@
         <f>SUMPRODUCT($AK23:$AR23,$AK$14:$AR$14)*IF($E23="CABA",'Parametros'!K$7,IF($E23="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN23" s="22" t="n">
-        <v>4.71</v>
+      <c r="AL23" s="22" t="n">
+        <v>1.082</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=0,9 × 114</t>
+          <t>Chapa LAF 1500 × 3000 e=2</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -22210,7 +22286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Pacheco Chapas</t>
+          <t>Pradecon S.A.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -22258,14 +22334,14 @@
         <f>SUMPRODUCT($AK24:$AR24,$AK$14:$AR$14)*IF($E24="CABA",'Parametros'!K$7,IF($E24="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK24" s="22" t="n">
-        <v>0.111</v>
+      <c r="AN24" s="22" t="n">
+        <v>4.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,25 × 106</t>
+          <t>Fleje e=0,9 × 114</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -22329,13 +22405,13 @@
         <v/>
       </c>
       <c r="AK25" s="22" t="n">
-        <v>0.103</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,25 × 200</t>
+          <t>Fleje e=1,25 × 106</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -22398,14 +22474,14 @@
         <f>SUMPRODUCT($AK26:$AR26,$AK$14:$AR$14)*IF($E26="CABA",'Parametros'!K$7,IF($E26="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL26" s="22" t="n">
-        <v>0.333</v>
+      <c r="AK26" s="22" t="n">
+        <v>0.103</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,6 × 200</t>
+          <t>Fleje e=1,25 × 200</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -22468,14 +22544,14 @@
         <f>SUMPRODUCT($AK27:$AR27,$AK$14:$AR$14)*IF($E27="CABA",'Parametros'!K$7,IF($E27="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM27" s="22" t="n">
-        <v>0.18</v>
+      <c r="AL27" s="22" t="n">
+        <v>0.333</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,6 × 250</t>
+          <t>Fleje e=1,6 × 200</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -22539,13 +22615,13 @@
         <v/>
       </c>
       <c r="AM28" s="22" t="n">
-        <v>0.224</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=1,6 × 300</t>
+          <t>Fleje e=1,6 × 250</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -22608,14 +22684,14 @@
         <f>SUMPRODUCT($AK29:$AR29,$AK$14:$AR$14)*IF($E29="CABA",'Parametros'!K$7,IF($E29="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN29" s="22" t="n">
-        <v>0.261</v>
+      <c r="AM29" s="22" t="n">
+        <v>0.224</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Fleje e=2 × 249</t>
+          <t>Fleje e=1,6 × 300</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -22679,18 +22755,18 @@
         <v/>
       </c>
       <c r="AN30" s="22" t="n">
-        <v>0.208</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Redondo SAE 1045 Ø25</t>
+          <t>Fleje e=2 × 249</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>barra 6 m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -22700,7 +22776,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Hierros Parrotta</t>
+          <t>Pacheco Chapas</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -22748,38 +22824,29 @@
         <f>SUMPRODUCT($AK31:$AR31,$AK$14:$AR$14)*IF($E31="CABA",'Parametros'!K$7,IF($E31="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO31" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AP31" s="22" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="AQ31" s="22" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AR31" s="22" t="n">
-        <v>0.1083</v>
+      <c r="AN31" s="22" t="n">
+        <v>0.208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø29 × 12,5 de alto, rosca M22x1,5, asiento Ø26</t>
+          <t>Redondo SAE 1045 Ø25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>barra 6 m</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Semielaborado comprado</t>
+          <t>Materia prima</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Eli-Met</t>
+          <t>Hierros Parrotta</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -22827,14 +22894,23 @@
         <f>SUMPRODUCT($AK32:$AR32,$AK$14:$AR$14)*IF($E32="CABA",'Parametros'!K$7,IF($E32="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK32" s="22" t="n">
-        <v>1</v>
+      <c r="AO32" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AP32" s="22" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="AQ32" s="22" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AR32" s="22" t="n">
+        <v>0.1083</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø36,8 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø29 × 12,5 de alto, rosca M22x1,5, asiento Ø26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -22897,14 +22973,14 @@
         <f>SUMPRODUCT($AK33:$AR33,$AK$14:$AR$14)*IF($E33="CABA",'Parametros'!K$7,IF($E33="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN33" s="22" t="n">
+      <c r="AK33" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø37 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø36,8 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -22967,14 +23043,14 @@
         <f>SUMPRODUCT($AK34:$AR34,$AK$14:$AR$14)*IF($E34="CABA",'Parametros'!K$7,IF($E34="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL34" s="22" t="n">
+      <c r="AN34" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø37 × 15 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø37 × 14 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -23037,14 +23113,14 @@
         <f>SUMPRODUCT($AK35:$AR35,$AK$14:$AR$14)*IF($E35="CABA",'Parametros'!K$7,IF($E35="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM35" s="22" t="n">
+      <c r="AL35" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø37 × 35 de alto, rosca M30x1,5, asiento Ø35</t>
+          <t>Cuello roscado — Ø37 × 15 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -23107,14 +23183,14 @@
         <f>SUMPRODUCT($AK36:$AR36,$AK$14:$AR$14)*IF($E36="CABA",'Parametros'!K$7,IF($E36="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO36" s="22" t="n">
+      <c r="AM36" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Cuello roscado — Ø88 × 37 de alto, rosca RBSP 2 1/2"-11 h, asiento Ø80</t>
+          <t>Cuello roscado — Ø37 × 35 de alto, rosca M30x1,5, asiento Ø35</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -23177,20 +23253,14 @@
         <f>SUMPRODUCT($AK37:$AR37,$AK$14:$AR$14)*IF($E37="CABA",'Parametros'!K$7,IF($E37="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR37" s="22" t="n">
+      <c r="AO37" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Cúpula — Ø276,5 × e3,2 × 94,4 de alto; disco Ø358,3</t>
+          <t>Cuello roscado — Ø88 × 37 de alto, rosca RBSP 2 1/2"-11 h, asiento Ø80</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -23205,7 +23275,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Gockel Ingeniería S.R.L.</t>
+          <t>Eli-Met</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -23253,14 +23323,20 @@
         <f>SUMPRODUCT($AK38:$AR38,$AK$14:$AR$14)*IF($E38="CABA",'Parametros'!K$7,IF($E38="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO38" s="22" t="n">
+      <c r="AP38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Cúpula — Ø320 × e3,2 × 109,9 de alto; disco Ø410,8</t>
+          <t>Cúpula — Ø276,5 × e3,2 × 94,4 de alto; disco Ø358,3</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -23323,14 +23399,14 @@
         <f>SUMPRODUCT($AK39:$AR39,$AK$14:$AR$14)*IF($E39="CABA",'Parametros'!K$7,IF($E39="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP39" s="22" t="n">
+      <c r="AO39" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Cúpula — Ø390 × e4,75 × 137,3 de alto; disco Ø507,3</t>
+          <t>Cúpula — Ø320 × e3,2 × 109,9 de alto; disco Ø410,8</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -23393,17 +23469,14 @@
         <f>SUMPRODUCT($AK40:$AR40,$AK$14:$AR$14)*IF($E40="CABA",'Parametros'!K$7,IF($E40="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ40" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR40" s="22" t="n">
+      <c r="AP40" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Fondo — Ø276,5 × e3,2 × 95 de alto; disco Ø362,5</t>
+          <t>Cúpula — Ø390 × e4,75 × 137,3 de alto; disco Ø507,3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -23466,14 +23539,17 @@
         <f>SUMPRODUCT($AK41:$AR41,$AK$14:$AR$14)*IF($E41="CABA",'Parametros'!K$7,IF($E41="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO41" s="22" t="n">
+      <c r="AQ41" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Fondo — Ø320 × e3,2 × 113 de alto; disco Ø423,5</t>
+          <t>Fondo — Ø276,5 × e3,2 × 95 de alto; disco Ø362,5</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -23536,14 +23612,14 @@
         <f>SUMPRODUCT($AK42:$AR42,$AK$14:$AR$14)*IF($E42="CABA",'Parametros'!K$7,IF($E42="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP42" s="22" t="n">
+      <c r="AO42" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Fondo — Ø390 × e4,75 × 139,8 de alto; disco Ø518,1</t>
+          <t>Fondo — Ø320 × e3,2 × 113 de alto; disco Ø423,5</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -23606,35 +23682,32 @@
         <f>SUMPRODUCT($AK43:$AR43,$AK$14:$AR$14)*IF($E43="CABA",'Parametros'!K$7,IF($E43="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ43" s="22" t="n">
+      <c r="AP43" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AR43" s="22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>Arandelas de tope (4) — 4 × Ø40 × Ø26 × 4</t>
-        </is>
-      </c>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Fondo — Ø390 × e4,75 × 139,8 de alto; disco Ø518,1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>Componente comprado</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr">
-        <is>
-          <t>Hierros Parrotta</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Semielaborado comprado</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Gockel Ingeniería S.R.L.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -23679,12 +23752,6 @@
         <f>SUMPRODUCT($AK44:$AR44,$AK$14:$AR$14)*IF($E44="CABA",'Parametros'!K$7,IF($E44="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO44" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP44" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ44" s="22" t="n">
         <v>1</v>
       </c>
@@ -23693,27 +23760,27 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Junta tórica de asiento — Ø24 ext. × cordón 3</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>Arandelas de tope (4) — 4 × Ø40 × Ø26 × 4</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Argensold</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>Hierros Parrotta</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -23758,14 +23825,23 @@
         <f>SUMPRODUCT($AK45:$AR45,$AK$14:$AR$14)*IF($E45="CABA",'Parametros'!K$7,IF($E45="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK45" s="22" t="n">
+      <c r="AO45" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP45" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ45" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento — Ø32,8 ext. × cordón 3</t>
+          <t>Junta tórica de asiento — Ø24 ext. × cordón 3</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -23828,23 +23904,14 @@
         <f>SUMPRODUCT($AK46:$AR46,$AK$14:$AR$14)*IF($E46="CABA",'Parametros'!K$7,IF($E46="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL46" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM46" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN46" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" s="22" t="n">
+      <c r="AK46" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento — Ø78 ext. × cordón 3</t>
+          <t>Junta tórica de asiento — Ø32,8 ext. × cordón 3</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -23907,20 +23974,23 @@
         <f>SUMPRODUCT($AK47:$AR47,$AK$14:$AR$14)*IF($E47="CABA",'Parametros'!K$7,IF($E47="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP47" s="22" t="n">
+      <c r="AL47" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ47" s="22" t="n">
+      <c r="AM47" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AR47" s="22" t="n">
+      <c r="AN47" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.037 de largo desarrollado</t>
+          <t>Junta tórica de asiento — Ø78 ext. × cordón 3</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -23935,7 +24005,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Argensold</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -23983,14 +24053,20 @@
         <f>SUMPRODUCT($AK48:$AR48,$AK$14:$AR$14)*IF($E48="CABA",'Parametros'!K$7,IF($E48="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO48" s="22" t="n">
+      <c r="AP48" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ48" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR48" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.305 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.037 de largo desarrollado</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -24053,14 +24129,14 @@
         <f>SUMPRODUCT($AK49:$AR49,$AK$14:$AR$14)*IF($E49="CABA",'Parametros'!K$7,IF($E49="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP49" s="22" t="n">
+      <c r="AO49" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.371 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.305 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -24123,14 +24199,14 @@
         <f>SUMPRODUCT($AK50:$AR50,$AK$14:$AR$14)*IF($E50="CABA",'Parametros'!K$7,IF($E50="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ50" s="22" t="n">
+      <c r="AP50" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado) — Ø25 × 1.714 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.371 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -24193,14 +24269,14 @@
         <f>SUMPRODUCT($AK51:$AR51,$AK$14:$AR$14)*IF($E51="CABA",'Parametros'!K$7,IF($E51="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR51" s="22" t="n">
+      <c r="AQ51" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
+          <t>Manguera (tramo enrollado) — Ø25 × 1.714 de largo desarrollado</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -24263,14 +24339,14 @@
         <f>SUMPRODUCT($AK52:$AR52,$AK$14:$AR$14)*IF($E52="CABA",'Parametros'!K$7,IF($E52="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO52" s="22" t="n">
+      <c r="AR52" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -24333,14 +24409,14 @@
         <f>SUMPRODUCT($AK53:$AR53,$AK$14:$AR$14)*IF($E53="CABA",'Parametros'!K$7,IF($E53="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP53" s="22" t="n">
+      <c r="AO53" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -24403,14 +24479,14 @@
         <f>SUMPRODUCT($AK54:$AR54,$AK$14:$AR$14)*IF($E54="CABA",'Parametros'!K$7,IF($E54="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ54" s="22" t="n">
+      <c r="AP54" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -24473,14 +24549,14 @@
         <f>SUMPRODUCT($AK55:$AR55,$AK$14:$AR$14)*IF($E55="CABA",'Parametros'!K$7,IF($E55="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR55" s="22" t="n">
+      <c r="AQ55" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -24543,14 +24619,14 @@
         <f>SUMPRODUCT($AK56:$AR56,$AK$14:$AR$14)*IF($E56="CABA",'Parametros'!K$7,IF($E56="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL56" s="22" t="n">
+      <c r="AR56" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -24613,14 +24689,14 @@
         <f>SUMPRODUCT($AK57:$AR57,$AK$14:$AR$14)*IF($E57="CABA",'Parametros'!K$7,IF($E57="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM57" s="22" t="n">
+      <c r="AL57" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 329 de largo desarrollado</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -24683,32 +24759,32 @@
         <f>SUMPRODUCT($AK58:$AR58,$AK$14:$AR$14)*IF($E58="CABA",'Parametros'!K$7,IF($E58="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN58" s="22" t="n">
+      <c r="AM58" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
-        <is>
-          <t>Manómetro — Ø36 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Manguera — Ø16 × 518 de largo desarrollado</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C59" s="24" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -24753,15 +24829,6 @@
         <f>SUMPRODUCT($AK59:$AR59,$AK$14:$AR$14)*IF($E59="CABA",'Parametros'!K$7,IF($E59="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK59" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL59" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM59" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AN59" s="22" t="n">
         <v>1</v>
       </c>
@@ -24769,7 +24836,7 @@
     <row r="60">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>Manómetro — Ø47 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
+          <t>Manómetro — Ø36 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
@@ -24832,23 +24899,23 @@
         <f>SUMPRODUCT($AK60:$AR60,$AK$14:$AR$14)*IF($E60="CABA",'Parametros'!K$7,IF($E60="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO60" s="22" t="n">
+      <c r="AK60" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AP60" s="22" t="n">
+      <c r="AL60" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ60" s="22" t="n">
+      <c r="AM60" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AR60" s="22" t="n">
+      <c r="AN60" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>Neumático macizo — Ø300 × 60 de ancho</t>
+          <t>Manómetro — Ø47 esfera, rango 0-3,5 MPa, sector verde en 1,4</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
@@ -24863,7 +24930,7 @@
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>Ruedar</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -24912,31 +24979,40 @@
         <v/>
       </c>
       <c r="AO61" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AP61" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ61" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR61" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Neumático macizo — Ø350 × 60 de ancho</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>Neumático macizo — Ø300 × 60 de ancho</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="24" t="inlineStr">
         <is>
           <t>Componente comprado</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="24" t="inlineStr">
         <is>
           <t>Ruedar</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="24" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -24981,17 +25057,14 @@
         <f>SUMPRODUCT($AK62:$AR62,$AK$14:$AR$14)*IF($E62="CABA",'Parametros'!K$7,IF($E62="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP62" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ62" s="22" t="n">
+      <c r="AO62" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
+          <t>Neumático macizo — Ø350 × 60 de ancho</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -25006,7 +25079,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Ruedar</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -25054,20 +25127,17 @@
         <f>SUMPRODUCT($AK63:$AR63,$AK$14:$AR$14)*IF($E63="CABA",'Parametros'!K$7,IF($E63="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL63" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM63" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN63" s="22" t="n">
-        <v>1</v>
+      <c r="AP63" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ63" s="22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Racor de manguera — 24 × 24 × 16</t>
+          <t>Racor de manguera — 19,4 × 18,8 × 18,8</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -25130,23 +25200,20 @@
         <f>SUMPRODUCT($AK64:$AR64,$AK$14:$AR$14)*IF($E64="CABA",'Parametros'!K$7,IF($E64="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO64" s="22" t="n">
+      <c r="AL64" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AP64" s="22" t="n">
+      <c r="AM64" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ64" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR64" s="22" t="n">
+      <c r="AN64" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Rueda con cubierta neumática — Ø400 × 100 de ancho</t>
+          <t>Racor de manguera — 24 × 24 × 16</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -25161,7 +25228,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Escanort S.A.</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -25209,14 +25276,23 @@
         <f>SUMPRODUCT($AK65:$AR65,$AK$14:$AR$14)*IF($E65="CABA",'Parametros'!K$7,IF($E65="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
+      <c r="AO65" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP65" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ65" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="AR65" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Suncho portatobera — 137,3 × 127 × 14,4</t>
+          <t>Rueda con cubierta neumática — Ø400 × 100 de ancho</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -25231,7 +25307,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Escanort S.A.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -25279,14 +25355,14 @@
         <f>SUMPRODUCT($AK66:$AR66,$AK$14:$AR$14)*IF($E66="CABA",'Parametros'!K$7,IF($E66="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL66" s="22" t="n">
-        <v>1</v>
+      <c r="AR66" s="22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Suncho portatobera — 166,3 × 156 × 14,4</t>
+          <t>Suncho portatobera — 137,6 × 127,6 × 14,4</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -25349,14 +25425,14 @@
         <f>SUMPRODUCT($AK67:$AR67,$AK$14:$AR$14)*IF($E67="CABA",'Parametros'!K$7,IF($E67="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM67" s="22" t="n">
+      <c r="AL67" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Suncho portatobera — 194,8 × 184,5 × 14,4</t>
+          <t>Suncho portatobera — 166,6 × 156,6 × 14,4</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -25419,14 +25495,14 @@
         <f>SUMPRODUCT($AK68:$AR68,$AK$14:$AR$14)*IF($E68="CABA",'Parametros'!K$7,IF($E68="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN68" s="22" t="n">
+      <c r="AM68" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Tobera campana — 200 × 68 × 68</t>
+          <t>Suncho portatobera — 195,1 × 185,1 × 14,4</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -25489,23 +25565,14 @@
         <f>SUMPRODUCT($AK69:$AR69,$AK$14:$AR$14)*IF($E69="CABA",'Parametros'!K$7,IF($E69="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO69" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP69" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ69" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR69" s="22" t="n">
+      <c r="AN69" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Tobera con portatobera — 73,5 × 19,9 × 19,9</t>
+          <t>Tobera campana — 200 × 68 × 68</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -25568,20 +25635,23 @@
         <f>SUMPRODUCT($AK70:$AR70,$AK$14:$AR$14)*IF($E70="CABA",'Parametros'!K$7,IF($E70="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL70" s="22" t="n">
+      <c r="AO70" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AM70" s="22" t="n">
+      <c r="AP70" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AN70" s="22" t="n">
+      <c r="AQ70" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR70" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Tobera — 12 × 12 × 10</t>
+          <t>Tobera con portatobera — 73,5 × 19,9 × 19,9</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -25644,14 +25714,20 @@
         <f>SUMPRODUCT($AK71:$AR71,$AK$14:$AR$14)*IF($E71="CABA",'Parametros'!K$7,IF($E71="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK71" s="22" t="n">
+      <c r="AL71" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM71" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN71" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada M-22 1 kg c/tubo de pesca plástico</t>
+          <t>Tobera — 12 × 12 × 10</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -25666,7 +25742,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -25721,7 +25797,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada M-30 c/resorte y tubo 7/8</t>
+          <t>Válvula HZ armada M-22 1 kg c/tubo de pesca plástico</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -25784,20 +25860,14 @@
         <f>SUMPRODUCT($AK73:$AR73,$AK$14:$AR$14)*IF($E73="CABA",'Parametros'!K$7,IF($E73="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL73" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM73" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN73" s="22" t="n">
+      <c r="AK73" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada de carro 25 kg c/traba, manija y resorte</t>
+          <t>Válvula HZ armada M-30 c/resorte y tubo 7/8</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -25860,14 +25930,20 @@
         <f>SUMPRODUCT($AK74:$AR74,$AK$14:$AR$14)*IF($E74="CABA",'Parametros'!K$7,IF($E74="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO74" s="22" t="n">
+      <c r="AL74" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM74" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN74" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Válvula HZ armada de carro 50-70-100 kg</t>
+          <t>Válvula HZ armada de carro 25 kg c/traba, manija y resorte</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -25930,20 +26006,14 @@
         <f>SUMPRODUCT($AK75:$AR75,$AK$14:$AR$14)*IF($E75="CABA",'Parametros'!K$7,IF($E75="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP75" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ75" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR75" s="22" t="n">
+      <c r="AO75" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Válvula esférica — 110 × 60 × 40</t>
+          <t>Válvula HZ armada de carro 50-70-100 kg</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -25958,7 +26028,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Yukon / MatafuegosYa S.R.L.</t>
+          <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -26006,9 +26076,6 @@
         <f>SUMPRODUCT($AK76:$AR76,$AK$14:$AR$14)*IF($E76="CABA",'Parametros'!K$7,IF($E76="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO76" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AP76" s="22" t="n">
         <v>1</v>
       </c>
@@ -26020,27 +26087,27 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="23" t="inlineStr">
-        <is>
-          <t>Alambre MAG ER70S-6 Ø0,9 (AWS A5.18)</t>
-        </is>
-      </c>
-      <c r="B77" s="23" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>Consumible de proceso</t>
-        </is>
-      </c>
-      <c r="D77" s="23" t="inlineStr">
-        <is>
-          <t>Conarco (ESAB Argentina)</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Válvula esférica — 110 × 60 × 40</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Componente comprado</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Yukon / MatafuegosYa S.R.L.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -26085,23 +26152,23 @@
         <f>SUMPRODUCT($AK77:$AR77,$AK$14:$AR$14)*IF($E77="CABA",'Parametros'!K$7,IF($E77="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK77" s="22" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="AL77" s="22" t="n">
-        <v>0.0292</v>
-      </c>
-      <c r="AM77" s="22" t="n">
-        <v>0.0551</v>
-      </c>
-      <c r="AN77" s="22" t="n">
-        <v>0.0985</v>
+      <c r="AO77" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP77" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ77" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR77" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>Alambre MAG ER70S-6 Ø1,0 (AWS A5.18)</t>
+          <t>Alambre MAG ER70S-6 Ø0,9 (AWS A5.18)</t>
         </is>
       </c>
       <c r="B78" s="23" t="inlineStr">
@@ -26164,28 +26231,28 @@
         <f>SUMPRODUCT($AK78:$AR78,$AK$14:$AR$14)*IF($E78="CABA",'Parametros'!K$7,IF($E78="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO78" s="22" t="n">
-        <v>0.3431</v>
-      </c>
-      <c r="AP78" s="22" t="n">
-        <v>0.4262</v>
-      </c>
-      <c r="AQ78" s="22" t="n">
-        <v>1.0749</v>
-      </c>
-      <c r="AR78" s="22" t="n">
-        <v>1.0956</v>
+      <c r="AK78" s="22" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="AL78" s="22" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="AM78" s="22" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AN78" s="22" t="n">
+        <v>0.0985</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t>Gas de protección MAG Arcal 21 / ARCAL Speed (Ar + 8 % CO₂, M20)</t>
+          <t>Alambre MAG ER70S-6 Ø1,0 (AWS A5.18)</t>
         </is>
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
@@ -26195,7 +26262,7 @@
       </c>
       <c r="D79" s="23" t="inlineStr">
         <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+          <t>Conarco (ESAB Argentina)</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
@@ -26243,53 +26310,41 @@
         <f>SUMPRODUCT($AK79:$AR79,$AK$14:$AR$14)*IF($E79="CABA",'Parametros'!K$7,IF($E79="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK79" s="22" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AL79" s="22" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="AM79" s="22" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="AN79" s="22" t="n">
-        <v>40.8</v>
-      </c>
       <c r="AO79" s="22" t="n">
-        <v>54.8</v>
+        <v>0.3431</v>
       </c>
       <c r="AP79" s="22" t="n">
-        <v>68.3</v>
+        <v>0.4262</v>
       </c>
       <c r="AQ79" s="22" t="n">
-        <v>79.5</v>
+        <v>1.0749</v>
       </c>
       <c r="AR79" s="22" t="n">
-        <v>84.59999999999999</v>
+        <v>1.0956</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="25" t="inlineStr">
-        <is>
-          <t>Granalla de acero S330 / S390 (ISO 11124-3, SAE J444)</t>
-        </is>
-      </c>
-      <c r="B80" s="25" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="C80" s="25" t="inlineStr">
+      <c r="A80" s="23" t="inlineStr">
+        <is>
+          <t>Gas de protección MAG Arcal 21 / ARCAL Speed (Ar + 8 % CO₂, M20)</t>
+        </is>
+      </c>
+      <c r="B80" s="23" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C80" s="23" t="inlineStr">
         <is>
           <t>Consumible de proceso</t>
         </is>
       </c>
-      <c r="D80" s="25" t="inlineStr">
-        <is>
-          <t>CyM Materiales</t>
-        </is>
-      </c>
-      <c r="E80" s="25" t="inlineStr">
+      <c r="D80" s="23" t="inlineStr">
+        <is>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+        </is>
+      </c>
+      <c r="E80" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -26335,40 +26390,52 @@
         <v/>
       </c>
       <c r="AK80" s="22" t="n">
-        <v>0.08</v>
+        <v>13.3</v>
       </c>
       <c r="AL80" s="22" t="n">
-        <v>0.08</v>
+        <v>27.1</v>
       </c>
       <c r="AM80" s="22" t="n">
-        <v>0.08</v>
+        <v>32.8</v>
       </c>
       <c r="AN80" s="22" t="n">
-        <v>0.08</v>
+        <v>40.8</v>
+      </c>
+      <c r="AO80" s="22" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AP80" s="22" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AQ80" s="22" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AR80" s="22" t="n">
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Servicio de pintura en polvo al horno, rojo 03-1-050</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Prymax</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>Granalla de acero S330 / S390 (ISO 11124-3, SAE J444)</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Consumible de proceso</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>CyM Materiales</t>
+        </is>
+      </c>
+      <c r="E81" s="25" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -26414,22 +26481,22 @@
         <v/>
       </c>
       <c r="AK81" s="22" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="AL81" s="22" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="AM81" s="22" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="AN81" s="22" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Servicio de pintura en polvo al horno, rojo 03-1-050 (con preparación por quemado)</t>
+          <t>Servicio de pintura en polvo al horno, rojo 03-1-050</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -26444,7 +26511,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Pintor de carros (cotización por mensaje)</t>
+          <t>Prymax</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -26492,41 +26559,41 @@
         <f>SUMPRODUCT($AK82:$AR82,$AK$14:$AR$14)*IF($E82="CABA",'Parametros'!K$7,IF($E82="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO82" s="22" t="n">
+      <c r="AK82" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AP82" s="22" t="n">
+      <c r="AL82" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ82" s="22" t="n">
+      <c r="AM82" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AR82" s="22" t="n">
+      <c r="AN82" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="23" t="inlineStr">
-        <is>
-          <t>Gas impulsor: N₂</t>
-        </is>
-      </c>
-      <c r="B83" s="23" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="C83" s="23" t="inlineStr">
-        <is>
-          <t>Carga (agente y gas)</t>
-        </is>
-      </c>
-      <c r="D83" s="23" t="inlineStr">
-        <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
-        </is>
-      </c>
-      <c r="E83" s="23" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de pintura en polvo al horno, rojo 03-1-050 (con preparación por quemado)</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Servicio</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Pintor de carros (cotización por mensaje)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -26571,35 +26638,23 @@
         <f>SUMPRODUCT($AK83:$AR83,$AK$14:$AR$14)*IF($E83="CABA",'Parametros'!K$7,IF($E83="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK83" s="22" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="AL83" s="22" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="AM83" s="22" t="n">
-        <v>0.0251</v>
-      </c>
-      <c r="AN83" s="22" t="n">
-        <v>0.0588</v>
-      </c>
       <c r="AO83" s="22" t="n">
-        <v>0.2013</v>
+        <v>1</v>
       </c>
       <c r="AP83" s="22" t="n">
-        <v>0.2819</v>
+        <v>1</v>
       </c>
       <c r="AQ83" s="22" t="n">
-        <v>0.5581</v>
+        <v>1</v>
       </c>
       <c r="AR83" s="22" t="n">
-        <v>0.5189</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t>Polvo químico seco ABC 60 (Sello IRAM 3569)</t>
+          <t>Gas impulsor: N₂</t>
         </is>
       </c>
       <c r="B84" s="23" t="inlineStr">
@@ -26614,7 +26669,7 @@
       </c>
       <c r="D84" s="23" t="inlineStr">
         <is>
-          <t>DEM S.A. (DEMSA)</t>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
@@ -26663,22 +26718,34 @@
         <v/>
       </c>
       <c r="AK84" s="22" t="n">
-        <v>1.05</v>
+        <v>0.0047</v>
       </c>
       <c r="AL84" s="22" t="n">
-        <v>2.55</v>
+        <v>0.0212</v>
       </c>
       <c r="AM84" s="22" t="n">
-        <v>5.15</v>
+        <v>0.0251</v>
       </c>
       <c r="AN84" s="22" t="n">
-        <v>10.15</v>
+        <v>0.0588</v>
+      </c>
+      <c r="AO84" s="22" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="AP84" s="22" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AQ84" s="22" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="AR84" s="22" t="n">
+        <v>0.5189</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>Polvo químico seco ABC 90 (Sello IRAM 3569)</t>
+          <t>Polvo químico seco ABC 60 (Sello IRAM 3569)</t>
         </is>
       </c>
       <c r="B85" s="23" t="inlineStr">
@@ -26741,41 +26808,41 @@
         <f>SUMPRODUCT($AK85:$AR85,$AK$14:$AR$14)*IF($E85="CABA",'Parametros'!K$7,IF($E85="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO85" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP85" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AQ85" s="22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AR85" s="22" t="n">
-        <v>100</v>
+      <c r="AK85" s="22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL85" s="22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM85" s="22" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AN85" s="22" t="n">
+        <v>10.15</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Estampilla IRAM de conformidad — 60 × 40</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Identificación</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>IRAM - Instituto Argentino de Normalización</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>Polvo químico seco ABC 90 (Sello IRAM 3569)</t>
+        </is>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C86" s="23" t="inlineStr">
+        <is>
+          <t>Carga (agente y gas)</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>DEM S.A. (DEMSA)</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -26820,35 +26887,23 @@
         <f>SUMPRODUCT($AK86:$AR86,$AK$14:$AR$14)*IF($E86="CABA",'Parametros'!K$7,IF($E86="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK86" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL86" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM86" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN86" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AO86" s="22" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AP86" s="22" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="AQ86" s="22" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="AR86" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 168 × 137 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Estampilla IRAM de conformidad — 60 × 40</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -26863,7 +26918,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>IRAM - Instituto Argentino de Normalización</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -26914,11 +26969,32 @@
       <c r="AK87" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="AL87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR87" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 234 × 152 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 168 × 137 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -26981,14 +27057,14 @@
         <f>SUMPRODUCT($AK88:$AR88,$AK$14:$AR$14)*IF($E88="CABA",'Parametros'!K$7,IF($E88="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL88" s="22" t="n">
+      <c r="AK88" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 289 × 144 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 234 × 152 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -27051,14 +27127,14 @@
         <f>SUMPRODUCT($AK89:$AR89,$AK$14:$AR$14)*IF($E89="CABA",'Parametros'!K$7,IF($E89="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM89" s="22" t="n">
+      <c r="AL89" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 343 × 224 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 289 × 144 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -27121,14 +27197,14 @@
         <f>SUMPRODUCT($AK90:$AR90,$AK$14:$AR$14)*IF($E90="CABA",'Parametros'!K$7,IF($E90="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AN90" s="22" t="n">
+      <c r="AM90" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 522 × 210 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 343 × 224 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -27191,14 +27267,14 @@
         <f>SUMPRODUCT($AK91:$AR91,$AK$14:$AR$14)*IF($E91="CABA",'Parametros'!K$7,IF($E91="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO91" s="22" t="n">
+      <c r="AN91" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 604 × 207 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 522 × 210 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -27261,14 +27337,14 @@
         <f>SUMPRODUCT($AK92:$AR92,$AK$14:$AR$14)*IF($E92="CABA",'Parametros'!K$7,IF($E92="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AP92" s="22" t="n">
+      <c r="AO92" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta / placa de características — 736 × 214 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
+          <t>Etiqueta / placa de características — 604 × 207 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -27331,17 +27407,14 @@
         <f>SUMPRODUCT($AK93:$AR93,$AK$14:$AR$14)*IF($E93="CABA",'Parametros'!K$7,IF($E93="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AQ93" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR93" s="22" t="n">
+      <c r="AP93" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de n° de serie GS1 — 45 × 25</t>
+          <t>Etiqueta / placa de características — 736 × 214 (desarrollo × alto: panel central 108° + 2 alas laterales), e ≈ 0,3, laminado UV</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -27404,24 +27477,6 @@
         <f>SUMPRODUCT($AK94:$AR94,$AK$14:$AR$14)*IF($E94="CABA",'Parametros'!K$7,IF($E94="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK94" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL94" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM94" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN94" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO94" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP94" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ94" s="22" t="n">
         <v>1</v>
       </c>
@@ -27432,7 +27487,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Faja de garantía válvula-cuello — 30 × 40</t>
+          <t>Etiqueta de n° de serie GS1 — 45 × 25</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -27523,7 +27578,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
+          <t>Faja de garantía válvula-cuello — 30 × 40</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -27538,12 +27593,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>PBA</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F96" s="21">
@@ -27614,7 +27669,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
+          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -27629,12 +27684,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>SonFuertes (vía Papelera Damián)</t>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>PBA</t>
         </is>
       </c>
       <c r="F97" s="21">
@@ -27705,7 +27760,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
+          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -27720,12 +27775,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Agencia Gubernamental de Control (CABA)</t>
+          <t>SonFuertes (vía Papelera Damián)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F98" s="21">
@@ -27768,6 +27823,9 @@
         <f>SUMPRODUCT($AK98:$AR98,$AK$14:$AR$14)*IF($E98="CABA",'Parametros'!K$7,IF($E98="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
+      <c r="AK98" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="AL98" s="22" t="n">
         <v>1</v>
       </c>
@@ -27793,7 +27851,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Soporte de pared (FL_ACC_01)</t>
+          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -27803,17 +27861,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Maxiseguridad</t>
+          <t>Agencia Gubernamental de Control (CABA)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>CABA</t>
         </is>
       </c>
       <c r="F99" s="21">
@@ -27865,11 +27923,23 @@
       <c r="AN99" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="AO99" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP99" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ99" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR99" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
+          <t>Soporte de pared (FL_ACC_01)</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -27932,14 +28002,20 @@
         <f>SUMPRODUCT($AK100:$AR100,$AK$14:$AR$14)*IF($E100="CABA",'Parametros'!K$7,IF($E100="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK100" s="22" t="n">
+      <c r="AL100" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM100" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN100" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Tornillo y tarugo de fijación</t>
+          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -27954,7 +28030,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Würth Argentina</t>
+          <t>Maxiseguridad</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -28002,20 +28078,14 @@
         <f>SUMPRODUCT($AK101:$AR101,$AK$14:$AR$14)*IF($E101="CABA",'Parametros'!K$7,IF($E101="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL101" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM101" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN101" s="22" t="n">
-        <v>2</v>
+      <c r="AK101" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 258 × 214 × 628 interior (envolvente del plano + 15 por lado)</t>
+          <t>Tornillo y tarugo de fijación</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -28025,12 +28095,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Würth Argentina</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -28078,14 +28148,20 @@
         <f>SUMPRODUCT($AK102:$AR102,$AK$14:$AR$14)*IF($E102="CABA",'Parametros'!K$7,IF($E102="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
+      <c r="AL102" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM102" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="AN102" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado doble — 258 × 215 × 628 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -28148,14 +28224,14 @@
         <f>SUMPRODUCT($AK103:$AR103,$AK$14:$AR$14)*IF($E103="CABA",'Parametros'!K$7,IF($E103="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK103" s="22" t="n">
+      <c r="AN103" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 229 × 157 × 379 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -28218,14 +28294,14 @@
         <f>SUMPRODUCT($AK104:$AR104,$AK$14:$AR$14)*IF($E104="CABA",'Parametros'!K$7,IF($E104="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL104" s="22" t="n">
+      <c r="AK104" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 244 × 186 × 455 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 229 × 158 × 379 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -28288,32 +28364,32 @@
         <f>SUMPRODUCT($AK105:$AR105,$AK$14:$AR$14)*IF($E105="CABA",'Parametros'!K$7,IF($E105="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AM105" s="22" t="n">
+      <c r="AL105" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="23" t="inlineStr">
-        <is>
-          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
-        </is>
-      </c>
-      <c r="B106" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="C106" s="23" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Caja de cartón corrugado simple — 244 × 187 × 455 interior (envolvente del plano + 15 por lado)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D106" s="23" t="inlineStr">
-        <is>
-          <t>MV Embalajes</t>
-        </is>
-      </c>
-      <c r="E106" s="23" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Maxipack</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -28358,41 +28434,32 @@
         <f>SUMPRODUCT($AK106:$AR106,$AK$14:$AR$14)*IF($E106="CABA",'Parametros'!K$7,IF($E106="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK106" s="22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL106" s="22" t="n">
-        <v>0.738</v>
-      </c>
       <c r="AM106" s="22" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="AN106" s="22" t="n">
-        <v>0.796</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
+        </is>
+      </c>
+      <c r="B107" s="23" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Maxipack</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="D107" s="23" t="inlineStr">
+        <is>
+          <t>MV Embalajes</t>
+        </is>
+      </c>
+      <c r="E107" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -28438,27 +28505,27 @@
         <v/>
       </c>
       <c r="AK107" s="22" t="n">
-        <v>0.0152</v>
+        <v>0.6</v>
       </c>
       <c r="AL107" s="22" t="n">
-        <v>0.0444</v>
+        <v>0.738</v>
       </c>
       <c r="AM107" s="22" t="n">
-        <v>0.0556</v>
+        <v>0.767</v>
       </c>
       <c r="AN107" s="22" t="n">
-        <v>0.125</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
+          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>jgo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -28468,7 +28535,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>MV Embalajes</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -28516,28 +28583,28 @@
         <f>SUMPRODUCT($AK108:$AR108,$AK$14:$AR$14)*IF($E108="CABA",'Parametros'!K$7,IF($E108="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO108" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP108" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ108" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR108" s="22" t="n">
-        <v>1</v>
+      <c r="AK108" s="22" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="AL108" s="22" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AM108" s="22" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="AN108" s="22" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de pallet (lote y destino, fracción)</t>
+          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>jgo</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -28547,7 +28614,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>MV Embalajes</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -28595,53 +28662,41 @@
         <f>SUMPRODUCT($AK109:$AR109,$AK$14:$AR$14)*IF($E109="CABA",'Parametros'!K$7,IF($E109="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK109" s="22" t="n">
-        <v>0.0038</v>
-      </c>
-      <c r="AL109" s="22" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="AM109" s="22" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="AN109" s="22" t="n">
-        <v>0.0312</v>
-      </c>
       <c r="AO109" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP109" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AQ109" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR109" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="23" t="inlineStr">
-        <is>
-          <t>Film stretch (fracción del pallet)</t>
-        </is>
-      </c>
-      <c r="B110" s="23" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="C110" s="23" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Etiqueta de pallet (lote y destino, fracción)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D110" s="23" t="inlineStr">
-        <is>
-          <t>MV Embalajes</t>
-        </is>
-      </c>
-      <c r="E110" s="23" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Astuprint</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -28687,52 +28742,52 @@
         <v/>
       </c>
       <c r="AK110" s="22" t="n">
-        <v>0.0005</v>
+        <v>0.0038</v>
       </c>
       <c r="AL110" s="22" t="n">
-        <v>0.0013</v>
+        <v>0.0111</v>
       </c>
       <c r="AM110" s="22" t="n">
-        <v>0.0017</v>
+        <v>0.0139</v>
       </c>
       <c r="AN110" s="22" t="n">
-        <v>0.0037</v>
+        <v>0.0312</v>
       </c>
       <c r="AO110" s="22" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="AP110" s="22" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="AQ110" s="22" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="AR110" s="22" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Instructivo de uso y mantenimiento</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="A111" s="23" t="inlineStr">
+        <is>
+          <t>Film stretch (fracción del pallet)</t>
+        </is>
+      </c>
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Astuprint</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="D111" s="23" t="inlineStr">
+        <is>
+          <t>MV Embalajes</t>
+        </is>
+      </c>
+      <c r="E111" s="23" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -28778,22 +28833,34 @@
         <v/>
       </c>
       <c r="AK111" s="22" t="n">
-        <v>1</v>
+        <v>0.0005</v>
       </c>
       <c r="AL111" s="22" t="n">
-        <v>1</v>
+        <v>0.0013</v>
       </c>
       <c r="AM111" s="22" t="n">
-        <v>1</v>
+        <v>0.0017</v>
       </c>
       <c r="AN111" s="22" t="n">
-        <v>1</v>
+        <v>0.0037</v>
+      </c>
+      <c r="AO111" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AP111" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AQ111" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AR111" s="22" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Pallet 1200 × 1000 (fracción)</t>
+          <t>Instructivo de uso y mantenimiento</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -28808,7 +28875,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>IndusPallets</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -28857,32 +28924,111 @@
         <v/>
       </c>
       <c r="AK112" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL112" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM112" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN112" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Pallet 1200 × 1000 (fracción)</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Embalaje</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>IndusPallets</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$5:$AR$5)*IF($E113="CABA",'Parametros'!B$7,IF($E113="PBA",1-'Parametros'!B$7,1))</f>
+        <v/>
+      </c>
+      <c r="G113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$6:$AR$6)*IF($E113="CABA",'Parametros'!C$7,IF($E113="PBA",1-'Parametros'!C$7,1))</f>
+        <v/>
+      </c>
+      <c r="H113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$7:$AR$7)*IF($E113="CABA",'Parametros'!D$7,IF($E113="PBA",1-'Parametros'!D$7,1))</f>
+        <v/>
+      </c>
+      <c r="I113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$8:$AR$8)*IF($E113="CABA",'Parametros'!E$7,IF($E113="PBA",1-'Parametros'!E$7,1))</f>
+        <v/>
+      </c>
+      <c r="J113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$9:$AR$9)*IF($E113="CABA",'Parametros'!F$7,IF($E113="PBA",1-'Parametros'!F$7,1))</f>
+        <v/>
+      </c>
+      <c r="K113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$10:$AR$10)*IF($E113="CABA",'Parametros'!G$7,IF($E113="PBA",1-'Parametros'!G$7,1))</f>
+        <v/>
+      </c>
+      <c r="L113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$11:$AR$11)*IF($E113="CABA",'Parametros'!H$7,IF($E113="PBA",1-'Parametros'!H$7,1))</f>
+        <v/>
+      </c>
+      <c r="M113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$12:$AR$12)*IF($E113="CABA",'Parametros'!I$7,IF($E113="PBA",1-'Parametros'!I$7,1))</f>
+        <v/>
+      </c>
+      <c r="N113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$13:$AR$13)*IF($E113="CABA",'Parametros'!J$7,IF($E113="PBA",1-'Parametros'!J$7,1))</f>
+        <v/>
+      </c>
+      <c r="O113" s="21">
+        <f>SUMPRODUCT($AK113:$AR113,$AK$14:$AR$14)*IF($E113="CABA",'Parametros'!K$7,IF($E113="PBA",1-'Parametros'!K$7,1))</f>
+        <v/>
+      </c>
+      <c r="AK113" s="22" t="n">
         <v>0.0038</v>
       </c>
-      <c r="AL112" s="22" t="n">
+      <c r="AL113" s="22" t="n">
         <v>0.0111</v>
       </c>
-      <c r="AM112" s="22" t="n">
+      <c r="AM113" s="22" t="n">
         <v>0.0139</v>
       </c>
-      <c r="AN112" s="22" t="n">
+      <c r="AN113" s="22" t="n">
         <v>0.0312</v>
       </c>
-      <c r="AO112" s="22" t="n">
+      <c r="AO113" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP112" s="22" t="n">
+      <c r="AP113" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="AQ112" s="22" t="n">
+      <c r="AQ113" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="AR112" s="22" t="n">
+      <c r="AR113" s="22" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A16:E112"/>
+  <autoFilter ref="A16:E113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/salida/mrp/MRP_MP.xlsx
+++ b/salida/mrp/MRP_MP.xlsx
@@ -20,12 +20,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MRP_CONSOLIDADO" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MP_MATAFUEGOS_FABRICADOS'!$A$16:$E$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MP_MATAFUEGOS_FABRICADOS'!$A$16:$E$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'MP_MATAFUEGOS_REVENDIDOS'!$A$16:$E$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'MP_CILINDROS'!$A$16:$E$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MP_SUSTITUTOS'!$A$16:$E$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'MP_RECARGAS'!$A$16:$E$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MRP_CONSOLIDADO'!$A$4:$E$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MRP_CONSOLIDADO'!$A$4:$E$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6240,7 +6240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -9148,7 +9148,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.900 de largo desarrollado</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.369 de largo desarrollado</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.600 de largo desarrollado</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 3.073 de largo desarrollado</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Válvula esférica — 110 × 60 × 40</t>
+          <t>Válvula esférica — cuerpo Ø40 × 56 con hexágonos 46, paso total, rosca a la manga y a la tobera; palanca 105 con empuñadura (cerrada: atravesada al caño)</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Faja de garantía válvula-cuello — 30 × 40</t>
+          <t>Faja de garantía válvula-cuello — 17 × 20 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -12364,7 +12364,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
+          <t>Faja de garantía válvula-cuello — 22 × 22 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
+          <t>Faja de garantía válvula-cuello — 22 × 23 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>SonFuertes (vía Papelera Damián)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -12498,7 +12498,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
+          <t>Faja de garantía válvula-cuello — 22 × 32 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -12513,59 +12513,59 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Agencia Gubernamental de Control (CABA)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_MATAFUEGOS_REVENDIDOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="G97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="H97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="I97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="J97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="K97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="L97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="M97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="N97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
       <c r="O97" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A97,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B97)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A97,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B97)</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Soporte de pared (FL_ACC_01)</t>
+          <t>Faja de garantía válvula-cuello — 30 × 47 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -12575,12 +12575,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Maxiseguridad</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
+          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Maxiseguridad</t>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -12699,7 +12699,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Tornillo y tarugo de fijación</t>
+          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Würth Argentina</t>
+          <t>SonFuertes (vía Papelera Damián)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -12766,7 +12766,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 212 × 212 × 582 interior (envolvente del plano + 15 por lado)</t>
+          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -12776,64 +12776,64 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Agencia Gubernamental de Control (CABA)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_MATAFUEGOS_REVENDIDOS</t>
         </is>
       </c>
       <c r="F101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="G101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="H101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="I101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="J101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="K101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="L101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="M101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="N101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
       <c r="O101" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A101,'MP_CILINDROS'!$B:$B,$B101)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A101,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B101)+SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A101,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B101)</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 258 × 215 × 628 interior (envolvente del plano + 15 por lado)</t>
+          <t>Soporte de pared (FL_ACC_01)</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Maxiseguridad</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 106 × 106 × 318 interior (envolvente del plano + 15 por lado)</t>
+          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -12910,64 +12910,64 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Maxiseguridad</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="G103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="H103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="I103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="J103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="K103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="L103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="M103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="N103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
       <c r="O103" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A103,'MP_CILINDROS'!$B:$B,$B103)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A103,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B103)</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 154 × 154 × 334 interior (envolvente del plano + 15 por lado)</t>
+          <t>Tornillo y tarugo de fijación</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -12977,64 +12977,64 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Würth Argentina</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="G104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="H104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="I104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="J104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="K104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="L104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="M104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="N104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
       <c r="O104" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A104,'MP_CILINDROS'!$B:$B,$B104)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A104,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B104)</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado doble — 212 × 212 × 582 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -13054,54 +13054,54 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="G105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="H105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="I105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="J105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="K105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="L105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="M105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="N105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
       <c r="O105" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A105,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B105)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A105,'MP_CILINDROS'!$B:$B,$B105)</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 183 × 183 × 410 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado doble — 258 × 215 × 628 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -13121,54 +13121,54 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="G106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="H106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="I106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="J106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="K106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="L106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="M106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="N106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
       <c r="O106" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A106,'MP_CILINDROS'!$B:$B,$B106)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A106,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B106)</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 229 × 158 × 379 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 106 × 106 × 318 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -13188,54 +13188,54 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="G107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="H107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="I107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="J107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="K107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="L107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="M107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="N107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
       <c r="O107" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A107,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B107)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A107,'MP_CILINDROS'!$B:$B,$B107)</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 244 × 187 × 455 interior (envolvente del plano + 15 por lado)</t>
+          <t>Caja de cartón corrugado simple — 154 × 154 × 334 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -13255,59 +13255,59 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="G108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="H108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="I108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="J108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="K108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="L108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="M108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="N108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
       <c r="O108" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A108,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B108)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A108,'MP_CILINDROS'!$B:$B,$B108)</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
+          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -13317,59 +13317,59 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>MV Embalajes</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="G109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="H109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="I109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="J109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="K109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="L109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="M109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="N109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
       <c r="O109" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A109,'MP_CILINDROS'!$B:$B,$B109)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A109,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B109)</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
+          <t>Caja de cartón corrugado simple — 183 × 183 × 410 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -13389,59 +13389,59 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="G110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="H110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="I110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="J110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="K110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="L110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="M110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="N110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
       <c r="O110" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A110,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B110)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A110,'MP_CILINDROS'!$B:$B,$B110)</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
+          <t>Caja de cartón corrugado simple — 229 × 158 × 379 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>jgo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -13451,59 +13451,59 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>MV Embalajes</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="G111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="H111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="I111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="J111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="K111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="L111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="M111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="N111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
       <c r="O111" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A111,'MP_CILINDROS'!$B:$B,$B111)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A111,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B111)</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de pallet (lote y destino, fracción)</t>
+          <t>Caja de cartón corrugado simple — 244 × 187 × 455 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -13518,64 +13518,64 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="G112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="H112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="I112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="J112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="K112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="L112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="M112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="N112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
       <c r="O112" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A112,'MP_CILINDROS'!$B:$B,$B112)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A112,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B112)</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Film stretch (fracción del pallet)</t>
+          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -13637,7 +13637,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Instructivo de uso y mantenimiento</t>
+          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -13652,64 +13652,64 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_FABRICADOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="G114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="H114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="I114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="J114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="K114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="L114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="M114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="N114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
       <c r="O114" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A114,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B114)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A114,'MP_CILINDROS'!$B:$B,$B114)</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Pallet 1200 × 1000 (fracción)</t>
+          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>jgo</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>IndusPallets</t>
+          <t>MV Embalajes</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -13771,7 +13771,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Separador de capa de cartón 1200 × 1000 (fracción del pallet)</t>
+          <t>Etiqueta de pallet (lote y destino, fracción)</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -13786,64 +13786,64 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="G116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="H116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="I116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="J116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="K116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="L116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="M116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="N116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
       <c r="O116" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A116,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B116)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A116,'MP_CILINDROS'!$B:$B,$B116)</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Tapón protector de rosca del cuello</t>
+          <t>Film stretch (fracción del pallet)</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -13853,59 +13853,59 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MV Embalajes</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>MP_CILINDROS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="G117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="H117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="I117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="J117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="K117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="L117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="M117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="N117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
       <c r="O117" s="21">
-        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A117,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B117)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A117,'MP_CILINDROS'!$B:$B,$B117)</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_10l</t>
+          <t>Instructivo de uso y mantenimiento</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -13915,64 +13915,64 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado</t>
+          <t>Embalaje</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Matafuegos Georgia - venta mayorista</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_REVENDIDOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS</t>
         </is>
       </c>
       <c r="F118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="G118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="H118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="I118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="J118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="K118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="L118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="M118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="N118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
       <c r="O118" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A118,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B118)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A118,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B118)</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_50l</t>
+          <t>Pallet 1200 × 1000 (fracción)</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -13982,64 +13982,64 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado</t>
+          <t>Embalaje</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Matafuegos Georgia - venta mayorista</t>
+          <t>IndusPallets</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_REVENDIDOS</t>
+          <t>MP_MATAFUEGOS_FABRICADOS, MP_CILINDROS</t>
         </is>
       </c>
       <c r="F119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!F:F,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="G119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!G:G,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="H119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!H:H,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="I119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!I:I,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="J119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!J:J,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="K119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!K:K,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="L119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!L:L,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="M119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!M:M,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="N119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!N:N,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
       <c r="O119" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A119,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B119)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_FABRICADOS'!O:O,'MP_MATAFUEGOS_FABRICADOS'!$A:$A,$A119,'MP_MATAFUEGOS_FABRICADOS'!$B:$B,$B119)+SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A119,'MP_CILINDROS'!$B:$B,$B119)</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AGUA_10l</t>
+          <t>Separador de capa de cartón 1200 × 1000 (fracción del pallet)</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -14049,64 +14049,64 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado</t>
+          <t>Embalaje</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Matafuegos Georgia - venta mayorista</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_REVENDIDOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="G120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="H120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="I120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="J120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="K120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="L120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="M120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="N120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
       <c r="O120" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A120,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B120)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A120,'MP_CILINDROS'!$B:$B,$B120)</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_BC_5kg</t>
+          <t>Tapón protector de rosca del cuello</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -14116,64 +14116,64 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado</t>
+          <t>Embalaje</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Matafuegos Georgia - venta mayorista</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>MP_MATAFUEGOS_REVENDIDOS</t>
+          <t>MP_CILINDROS</t>
         </is>
       </c>
       <c r="F121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!F:F,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="G121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!G:G,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="H121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!H:H,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="I121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!I:I,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="J121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!J:J,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="K121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!K:K,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="L121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!L:L,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="M121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!M:M,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="N121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!N:N,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
       <c r="O121" s="21">
-        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A121,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B121)</f>
+        <f>SUMIFS('MP_CILINDROS'!O:O,'MP_CILINDROS'!$A:$A,$A121,'MP_CILINDROS'!$B:$B,$B121)</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CLASED_9l</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_10l</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -14240,7 +14240,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_2kg</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AFFF_50l</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Mozart S.R.L.</t>
+          <t>Matafuegos Georgia - venta mayorista</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -14307,7 +14307,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_5kg</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_AGUA_10l</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Mozart S.R.L.</t>
+          <t>Matafuegos Georgia - venta mayorista</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_HCFC-HFC_5kg</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_BC_5kg</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -14441,7 +14441,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_SALESK_6l</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CLASED_9l</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -14508,141 +14508,141 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Acetato de potasio - DEMSA Kitchen (IRAM 3697)</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_2kg</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Recarga y mantenimiento</t>
+          <t>Equipo terminado comprado</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>Mozart S.R.L.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>MP_RECARGAS</t>
+          <t>MP_MATAFUEGOS_REVENDIDOS</t>
         </is>
       </c>
       <c r="F127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="G127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="H127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="I127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="J127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="K127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="L127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="M127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="N127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
       <c r="O127" s="21">
-        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A127,'MP_RECARGAS'!$B:$B,$B127)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A127,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B127)</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Concentrado espumígeno AFFF 3 % (IRAM 3515)</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_CO2_5kg</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Recarga y mantenimiento</t>
+          <t>Equipo terminado comprado</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>DEM S.A. (DEMSA)</t>
+          <t>Mozart S.R.L.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>MP_RECARGAS</t>
+          <t>MP_MATAFUEGOS_REVENDIDOS</t>
         </is>
       </c>
       <c r="F128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="G128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="H128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="I128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="J128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="K128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="L128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="M128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="N128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
       <c r="O128" s="21">
-        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A128,'MP_RECARGAS'!$B:$B,$B128)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A128,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B128)</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Disco de seguridad</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_HCFC-HFC_5kg</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -14652,136 +14652,136 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Recarga y mantenimiento</t>
+          <t>Equipo terminado comprado</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>Matafuegos Georgia - venta mayorista</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>MP_RECARGAS</t>
+          <t>MP_MATAFUEGOS_REVENDIDOS</t>
         </is>
       </c>
       <c r="F129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="G129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="H129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="I129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="J129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="K129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="L129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="M129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="N129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
       <c r="O129" s="21">
-        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A129,'MP_RECARGAS'!$B:$B,$B129)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A129,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B129)</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Dióxido de carbono (IRAM 41170)</t>
+          <t>Equipo terminado comprado (fabricante con Sello IRAM): FL_MAT_SALESK_6l</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Recarga y mantenimiento</t>
+          <t>Equipo terminado comprado</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+          <t>Matafuegos Georgia - venta mayorista</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>MP_RECARGAS</t>
+          <t>MP_MATAFUEGOS_REVENDIDOS</t>
         </is>
       </c>
       <c r="F130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!F:F,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="G130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!G:G,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="H130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!H:H,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="I130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!I:I,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="J130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!J:J,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="K130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!K:K,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="L130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!L:L,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="M130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!M:M,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="N130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!N:N,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
       <c r="O130" s="21">
-        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A130,'MP_RECARGAS'!$B:$B,$B130)</f>
+        <f>SUMIFS('MP_MATAFUEGOS_REVENDIDOS'!O:O,'MP_MATAFUEGOS_REVENDIDOS'!$A:$A,$A130,'MP_MATAFUEGOS_REVENDIDOS'!$B:$B,$B130)</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de servicio del recargador (extintor n°, serie, próxima recarga y PH)</t>
+          <t>Acetato de potasio - DEMSA Kitchen (IRAM 3697)</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -14843,12 +14843,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Gas impulsor: Argón</t>
+          <t>Concentrado espumígeno AFFF 3 % (IRAM 3515)</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Air Liquide Argentina - sucursal Piñeyro</t>
+          <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>HCFC 123 / HFC 236fa (agente limpio)</t>
+          <t>Disco de seguridad</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Polvex S.R.L. / Sancibrao</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -14977,12 +14977,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento del cuello</t>
+          <t>Dióxido de carbono (IRAM 41170)</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Argensold</t>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -15044,7 +15044,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Marbete (anillo, color del año)</t>
+          <t>Etiqueta de servicio del recargador (extintor n°, serie, próxima recarga y PH)</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -15111,12 +15111,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Oblea PBA de recarga Ø46 + estampilla precinto 1" × 200 mm válvula-cuerpo</t>
+          <t>Gas impulsor: Argón</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Air Liquide Argentina - sucursal Piñeyro</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -15178,7 +15178,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Polvo para metales combustibles clase D</t>
+          <t>HCFC 123 / HFC 236fa (agente limpio)</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>DEM S.A. (DEMSA)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -15245,12 +15245,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Polvo químico seco BC (bicarbonato)</t>
+          <t>Junta tórica de asiento del cuello</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Polvex S.R.L. / Sancibrao</t>
+          <t>Argensold</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Precinto plástico numerado, color, con nombre del recargador</t>
+          <t>Marbete (anillo, color del año)</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>SonFuertes (vía Papelera Damián)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -15379,7 +15379,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación AGC (módulo papel con QR + etiqueta AGC)</t>
+          <t>Oblea PBA de recarga Ø46 + estampilla precinto 1" × 200 mm válvula-cuerpo</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Agencia Gubernamental de Control (CABA)</t>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -15446,12 +15446,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación DPS de revisión / recarga</t>
+          <t>Polvo para metales combustibles clase D</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>DEM S.A. (DEMSA)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -15510,8 +15510,276 @@
         <v/>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Polvo químico seco BC (bicarbonato)</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Recarga y mantenimiento</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Polvex S.R.L. / Sancibrao</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>MP_RECARGAS</t>
+        </is>
+      </c>
+      <c r="F142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="G142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="H142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="I142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="J142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="K142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="L142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="M142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="N142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+      <c r="O142" s="21">
+        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A142,'MP_RECARGAS'!$B:$B,$B142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Precinto plástico numerado, color, con nombre del recargador</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Recarga y mantenimiento</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>SonFuertes (vía Papelera Damián)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>MP_RECARGAS</t>
+        </is>
+      </c>
+      <c r="F143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="G143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="H143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="I143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="J143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="K143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="L143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="M143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="N143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+      <c r="O143" s="21">
+        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A143,'MP_RECARGAS'!$B:$B,$B143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de identificación AGC (módulo papel con QR + etiqueta AGC)</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Recarga y mantenimiento</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Agencia Gubernamental de Control (CABA)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>MP_RECARGAS</t>
+        </is>
+      </c>
+      <c r="F144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="G144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="H144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="I144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="J144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="K144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="L144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="M144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="N144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+      <c r="O144" s="21">
+        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A144,'MP_RECARGAS'!$B:$B,$B144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de identificación DPS de revisión / recarga</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Recarga y mantenimiento</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>MP_RECARGAS</t>
+        </is>
+      </c>
+      <c r="F145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!F:F,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="G145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!G:G,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="H145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!H:H,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="I145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!I:I,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="J145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!J:J,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="K145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!K:K,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="L145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!L:L,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="M145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!M:M,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="N145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!N:N,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+      <c r="O145" s="21">
+        <f>SUMIFS('MP_RECARGAS'!O:O,'MP_RECARGAS'!$A:$A,$A145,'MP_RECARGAS'!$B:$B,$B145)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E141"/>
+  <autoFilter ref="A4:E145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21186,7 +21454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR113"/>
+  <dimension ref="A1:AR117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -21821,16 +22089,16 @@
         <v/>
       </c>
       <c r="AO17" s="22" t="n">
-        <v>0.2666</v>
+        <v>0.2606</v>
       </c>
       <c r="AP17" s="22" t="n">
-        <v>0.2615</v>
+        <v>0.2555</v>
       </c>
       <c r="AQ17" s="22" t="n">
-        <v>0.3071</v>
+        <v>0.3011</v>
       </c>
       <c r="AR17" s="22" t="n">
-        <v>0.2784</v>
+        <v>0.2723</v>
       </c>
     </row>
     <row r="18">
@@ -24346,7 +24614,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 1.698 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 1.900 de largo desarrollado</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -24416,7 +24684,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.168 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.369 de largo desarrollado</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -24486,7 +24754,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.398 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 2.600 de largo desarrollado</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -24556,7 +24824,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 2.871 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -24619,14 +24887,14 @@
         <f>SUMPRODUCT($AK56:$AR56,$AK$14:$AR$14)*IF($E56="CABA",'Parametros'!K$7,IF($E56="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AR56" s="22" t="n">
+      <c r="AL56" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Manguera — Ø16 × 238 de largo desarrollado</t>
+          <t>Manguera — Ø16 × 3.073 de largo desarrollado</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -24689,7 +24957,7 @@
         <f>SUMPRODUCT($AK57:$AR57,$AK$14:$AR$14)*IF($E57="CABA",'Parametros'!K$7,IF($E57="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL57" s="22" t="n">
+      <c r="AR57" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26089,7 +26357,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Válvula esférica — 110 × 60 × 40</t>
+          <t>Válvula esférica — cuerpo Ø40 × 56 con hexágonos 46, paso total, rosca a la manga y a la tobera; palanca 105 con empuñadura (cerrada: atravesada al caño)</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -27578,7 +27846,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Faja de garantía válvula-cuello — 30 × 40</t>
+          <t>Faja de garantía válvula-cuello — 17 × 20 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -27644,32 +27912,11 @@
       <c r="AK96" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AL96" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM96" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN96" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO96" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP96" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ96" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR96" s="22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
+          <t>Faja de garantía válvula-cuello — 22 × 22 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -27684,12 +27931,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>PBA</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F97" s="21">
@@ -27732,35 +27979,17 @@
         <f>SUMPRODUCT($AK97:$AR97,$AK$14:$AR$14)*IF($E97="CABA",'Parametros'!K$7,IF($E97="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK97" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AL97" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AM97" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AN97" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AO97" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP97" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ97" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR97" s="22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
+          <t>Faja de garantía válvula-cuello — 22 × 23 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -27775,7 +28004,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>SonFuertes (vía Papelera Damián)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -27823,35 +28052,14 @@
         <f>SUMPRODUCT($AK98:$AR98,$AK$14:$AR$14)*IF($E98="CABA",'Parametros'!K$7,IF($E98="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK98" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL98" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AM98" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AN98" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO98" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP98" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ98" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR98" s="22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
+          <t>Faja de garantía válvula-cuello — 22 × 32 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -27866,12 +28074,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Agencia Gubernamental de Control (CABA)</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F99" s="21">
@@ -27914,32 +28122,14 @@
         <f>SUMPRODUCT($AK99:$AR99,$AK$14:$AR$14)*IF($E99="CABA",'Parametros'!K$7,IF($E99="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL99" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM99" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN99" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="AO99" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AP99" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ99" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR99" s="22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Soporte de pared (FL_ACC_01)</t>
+          <t>Faja de garantía válvula-cuello — 30 × 47 (ancho × largo desarrollado), pegada sobre la unión: cuerpo de la válvula, tuerca y cuello</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -27949,12 +28139,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Maxiseguridad</t>
+          <t>Astuprint</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -28002,20 +28192,20 @@
         <f>SUMPRODUCT($AK100:$AR100,$AK$14:$AR$14)*IF($E100="CABA",'Parametros'!K$7,IF($E100="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL100" s="22" t="n">
+      <c r="AP100" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AM100" s="22" t="n">
+      <c r="AQ100" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AN100" s="22" t="n">
+      <c r="AR100" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
+          <t>Oblea de fabricación (PBA) — Ø46 (Res. OPDS 522/07), numerada, autodestructible</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -28025,17 +28215,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Maxiseguridad</t>
+          <t>Ministerio de Ambiente PBA (ex OPDS)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>PBA</t>
         </is>
       </c>
       <c r="F101" s="21">
@@ -28081,11 +28271,32 @@
       <c r="AK101" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="AL101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR101" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Tornillo y tarugo de fijación</t>
+          <t>Precinto de fábrica — Ø5 × 10, numerado, rotura 30-50 N</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -28095,12 +28306,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Soporte</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Würth Argentina</t>
+          <t>SonFuertes (vía Papelera Damián)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -28148,20 +28359,35 @@
         <f>SUMPRODUCT($AK102:$AR102,$AK$14:$AR$14)*IF($E102="CABA",'Parametros'!K$7,IF($E102="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
+      <c r="AK102" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="AL102" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM102" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN102" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AO102" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP102" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ102" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR102" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado doble — 258 × 215 × 628 interior (envolvente del plano + 15 por lado)</t>
+          <t>Tarjeta de identificación AGC (CABA) — 140 × 55</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -28171,17 +28397,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Agencia Gubernamental de Control (CABA)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>CABA</t>
         </is>
       </c>
       <c r="F103" s="21">
@@ -28224,14 +28450,32 @@
         <f>SUMPRODUCT($AK103:$AR103,$AK$14:$AR$14)*IF($E103="CABA",'Parametros'!K$7,IF($E103="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
+      <c r="AL103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM103" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="AN103" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="AO103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR103" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
+          <t>Soporte de pared (FL_ACC_01)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -28241,12 +28485,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Maxiseguridad</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -28294,14 +28538,20 @@
         <f>SUMPRODUCT($AK104:$AR104,$AK$14:$AR$14)*IF($E104="CABA",'Parametros'!K$7,IF($E104="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK104" s="22" t="n">
+      <c r="AL104" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM104" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN104" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 229 × 158 × 379 interior (envolvente del plano + 15 por lado)</t>
+          <t>Soporte vehicular con cierre rápido (FL_ACC_02)</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -28311,12 +28561,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Maxiseguridad</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -28364,14 +28614,14 @@
         <f>SUMPRODUCT($AK105:$AR105,$AK$14:$AR$14)*IF($E105="CABA",'Parametros'!K$7,IF($E105="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AL105" s="22" t="n">
+      <c r="AK105" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Caja de cartón corrugado simple — 244 × 187 × 455 interior (envolvente del plano + 15 por lado)</t>
+          <t>Tornillo y tarugo de fijación</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -28381,12 +28631,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Embalaje</t>
+          <t>Soporte</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Maxipack</t>
+          <t>Würth Argentina</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -28434,32 +28684,38 @@
         <f>SUMPRODUCT($AK106:$AR106,$AK$14:$AR$14)*IF($E106="CABA",'Parametros'!K$7,IF($E106="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
+      <c r="AL106" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="AM106" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AN106" s="22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="23" t="inlineStr">
-        <is>
-          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
-        </is>
-      </c>
-      <c r="B107" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="C107" s="23" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Caja de cartón corrugado doble — 258 × 215 × 628 interior (envolvente del plano + 15 por lado)</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Embalaje</t>
         </is>
       </c>
-      <c r="D107" s="23" t="inlineStr">
-        <is>
-          <t>MV Embalajes</t>
-        </is>
-      </c>
-      <c r="E107" s="23" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Maxipack</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -28504,23 +28760,14 @@
         <f>SUMPRODUCT($AK107:$AR107,$AK$14:$AR$14)*IF($E107="CABA",'Parametros'!K$7,IF($E107="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK107" s="22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL107" s="22" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="AM107" s="22" t="n">
-        <v>0.767</v>
-      </c>
       <c r="AN107" s="22" t="n">
-        <v>0.796</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
+          <t>Caja de cartón corrugado simple — 160 × 107 × 347 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -28584,27 +28831,18 @@
         <v/>
       </c>
       <c r="AK108" s="22" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="AL108" s="22" t="n">
-        <v>0.0444</v>
-      </c>
-      <c r="AM108" s="22" t="n">
-        <v>0.0556</v>
-      </c>
-      <c r="AN108" s="22" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
+          <t>Caja de cartón corrugado simple — 229 × 158 × 379 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>jgo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -28614,7 +28852,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>MV Embalajes</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -28662,23 +28900,14 @@
         <f>SUMPRODUCT($AK109:$AR109,$AK$14:$AR$14)*IF($E109="CABA",'Parametros'!K$7,IF($E109="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AO109" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP109" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ109" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR109" s="22" t="n">
+      <c r="AL109" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Etiqueta de pallet (lote y destino, fracción)</t>
+          <t>Caja de cartón corrugado simple — 244 × 187 × 455 interior (envolvente del plano + 15 por lado)</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -28693,7 +28922,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -28741,40 +28970,19 @@
         <f>SUMPRODUCT($AK110:$AR110,$AK$14:$AR$14)*IF($E110="CABA",'Parametros'!K$7,IF($E110="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK110" s="22" t="n">
-        <v>0.0038</v>
-      </c>
-      <c r="AL110" s="22" t="n">
-        <v>0.0111</v>
-      </c>
       <c r="AM110" s="22" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="AN110" s="22" t="n">
-        <v>0.0312</v>
-      </c>
-      <c r="AO110" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP110" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ110" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR110" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="23" t="inlineStr">
         <is>
-          <t>Film stretch (fracción del pallet)</t>
+          <t>Cinta de embalaje PP 48 mm (cierre de la caja)</t>
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C111" s="23" t="inlineStr">
@@ -28833,34 +29041,22 @@
         <v/>
       </c>
       <c r="AK111" s="22" t="n">
-        <v>0.0005</v>
+        <v>0.6</v>
       </c>
       <c r="AL111" s="22" t="n">
-        <v>0.0013</v>
+        <v>0.738</v>
       </c>
       <c r="AM111" s="22" t="n">
-        <v>0.0017</v>
+        <v>0.767</v>
       </c>
       <c r="AN111" s="22" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="AO111" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AP111" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AQ111" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AR111" s="22" t="n">
-        <v>0.12</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Instructivo de uso y mantenimiento</t>
+          <t>Esquineros de cartón 50 × 50 × 1200 (fracción del pallet)</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -28875,7 +29071,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Astuprint</t>
+          <t>Maxipack</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -28924,27 +29120,27 @@
         <v/>
       </c>
       <c r="AK112" s="22" t="n">
-        <v>1</v>
+        <v>0.0152</v>
       </c>
       <c r="AL112" s="22" t="n">
-        <v>1</v>
+        <v>0.0444</v>
       </c>
       <c r="AM112" s="22" t="n">
-        <v>1</v>
+        <v>0.0556</v>
       </c>
       <c r="AN112" s="22" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Pallet 1200 × 1000 (fracción)</t>
+          <t>Esquineros y funda de polietileno — a medida de la envolvente del plano</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>jgo</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -28954,7 +29150,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>IndusPallets</t>
+          <t>MV Embalajes</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -29002,33 +29198,373 @@
         <f>SUMPRODUCT($AK113:$AR113,$AK$14:$AR$14)*IF($E113="CABA",'Parametros'!K$7,IF($E113="PBA",1-'Parametros'!K$7,1))</f>
         <v/>
       </c>
-      <c r="AK113" s="22" t="n">
-        <v>0.0038</v>
-      </c>
-      <c r="AL113" s="22" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="AM113" s="22" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="AN113" s="22" t="n">
-        <v>0.0312</v>
-      </c>
       <c r="AO113" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP113" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AQ113" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR113" s="22" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Etiqueta de pallet (lote y destino, fracción)</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Embalaje</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Astuprint</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$5:$AR$5)*IF($E114="CABA",'Parametros'!B$7,IF($E114="PBA",1-'Parametros'!B$7,1))</f>
+        <v/>
+      </c>
+      <c r="G114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$6:$AR$6)*IF($E114="CABA",'Parametros'!C$7,IF($E114="PBA",1-'Parametros'!C$7,1))</f>
+        <v/>
+      </c>
+      <c r="H114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$7:$AR$7)*IF($E114="CABA",'Parametros'!D$7,IF($E114="PBA",1-'Parametros'!D$7,1))</f>
+        <v/>
+      </c>
+      <c r="I114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$8:$AR$8)*IF($E114="CABA",'Parametros'!E$7,IF($E114="PBA",1-'Parametros'!E$7,1))</f>
+        <v/>
+      </c>
+      <c r="J114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$9:$AR$9)*IF($E114="CABA",'Parametros'!F$7,IF($E114="PBA",1-'Parametros'!F$7,1))</f>
+        <v/>
+      </c>
+      <c r="K114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$10:$AR$10)*IF($E114="CABA",'Parametros'!G$7,IF($E114="PBA",1-'Parametros'!G$7,1))</f>
+        <v/>
+      </c>
+      <c r="L114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$11:$AR$11)*IF($E114="CABA",'Parametros'!H$7,IF($E114="PBA",1-'Parametros'!H$7,1))</f>
+        <v/>
+      </c>
+      <c r="M114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$12:$AR$12)*IF($E114="CABA",'Parametros'!I$7,IF($E114="PBA",1-'Parametros'!I$7,1))</f>
+        <v/>
+      </c>
+      <c r="N114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$13:$AR$13)*IF($E114="CABA",'Parametros'!J$7,IF($E114="PBA",1-'Parametros'!J$7,1))</f>
+        <v/>
+      </c>
+      <c r="O114" s="21">
+        <f>SUMPRODUCT($AK114:$AR114,$AK$14:$AR$14)*IF($E114="CABA",'Parametros'!K$7,IF($E114="PBA",1-'Parametros'!K$7,1))</f>
+        <v/>
+      </c>
+      <c r="AK114" s="22" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="AL114" s="22" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="AM114" s="22" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="AN114" s="22" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="AO114" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP114" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ114" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR114" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="23" t="inlineStr">
+        <is>
+          <t>Film stretch (fracción del pallet)</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C115" s="23" t="inlineStr">
+        <is>
+          <t>Embalaje</t>
+        </is>
+      </c>
+      <c r="D115" s="23" t="inlineStr">
+        <is>
+          <t>MV Embalajes</t>
+        </is>
+      </c>
+      <c r="E115" s="23" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$5:$AR$5)*IF($E115="CABA",'Parametros'!B$7,IF($E115="PBA",1-'Parametros'!B$7,1))</f>
+        <v/>
+      </c>
+      <c r="G115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$6:$AR$6)*IF($E115="CABA",'Parametros'!C$7,IF($E115="PBA",1-'Parametros'!C$7,1))</f>
+        <v/>
+      </c>
+      <c r="H115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$7:$AR$7)*IF($E115="CABA",'Parametros'!D$7,IF($E115="PBA",1-'Parametros'!D$7,1))</f>
+        <v/>
+      </c>
+      <c r="I115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$8:$AR$8)*IF($E115="CABA",'Parametros'!E$7,IF($E115="PBA",1-'Parametros'!E$7,1))</f>
+        <v/>
+      </c>
+      <c r="J115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$9:$AR$9)*IF($E115="CABA",'Parametros'!F$7,IF($E115="PBA",1-'Parametros'!F$7,1))</f>
+        <v/>
+      </c>
+      <c r="K115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$10:$AR$10)*IF($E115="CABA",'Parametros'!G$7,IF($E115="PBA",1-'Parametros'!G$7,1))</f>
+        <v/>
+      </c>
+      <c r="L115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$11:$AR$11)*IF($E115="CABA",'Parametros'!H$7,IF($E115="PBA",1-'Parametros'!H$7,1))</f>
+        <v/>
+      </c>
+      <c r="M115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$12:$AR$12)*IF($E115="CABA",'Parametros'!I$7,IF($E115="PBA",1-'Parametros'!I$7,1))</f>
+        <v/>
+      </c>
+      <c r="N115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$13:$AR$13)*IF($E115="CABA",'Parametros'!J$7,IF($E115="PBA",1-'Parametros'!J$7,1))</f>
+        <v/>
+      </c>
+      <c r="O115" s="21">
+        <f>SUMPRODUCT($AK115:$AR115,$AK$14:$AR$14)*IF($E115="CABA",'Parametros'!K$7,IF($E115="PBA",1-'Parametros'!K$7,1))</f>
+        <v/>
+      </c>
+      <c r="AK115" s="22" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AL115" s="22" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="AM115" s="22" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AN115" s="22" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="AO115" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AP115" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AQ115" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AR115" s="22" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Instructivo de uso y mantenimiento</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Embalaje</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Astuprint</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$5:$AR$5)*IF($E116="CABA",'Parametros'!B$7,IF($E116="PBA",1-'Parametros'!B$7,1))</f>
+        <v/>
+      </c>
+      <c r="G116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$6:$AR$6)*IF($E116="CABA",'Parametros'!C$7,IF($E116="PBA",1-'Parametros'!C$7,1))</f>
+        <v/>
+      </c>
+      <c r="H116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$7:$AR$7)*IF($E116="CABA",'Parametros'!D$7,IF($E116="PBA",1-'Parametros'!D$7,1))</f>
+        <v/>
+      </c>
+      <c r="I116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$8:$AR$8)*IF($E116="CABA",'Parametros'!E$7,IF($E116="PBA",1-'Parametros'!E$7,1))</f>
+        <v/>
+      </c>
+      <c r="J116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$9:$AR$9)*IF($E116="CABA",'Parametros'!F$7,IF($E116="PBA",1-'Parametros'!F$7,1))</f>
+        <v/>
+      </c>
+      <c r="K116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$10:$AR$10)*IF($E116="CABA",'Parametros'!G$7,IF($E116="PBA",1-'Parametros'!G$7,1))</f>
+        <v/>
+      </c>
+      <c r="L116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$11:$AR$11)*IF($E116="CABA",'Parametros'!H$7,IF($E116="PBA",1-'Parametros'!H$7,1))</f>
+        <v/>
+      </c>
+      <c r="M116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$12:$AR$12)*IF($E116="CABA",'Parametros'!I$7,IF($E116="PBA",1-'Parametros'!I$7,1))</f>
+        <v/>
+      </c>
+      <c r="N116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$13:$AR$13)*IF($E116="CABA",'Parametros'!J$7,IF($E116="PBA",1-'Parametros'!J$7,1))</f>
+        <v/>
+      </c>
+      <c r="O116" s="21">
+        <f>SUMPRODUCT($AK116:$AR116,$AK$14:$AR$14)*IF($E116="CABA",'Parametros'!K$7,IF($E116="PBA",1-'Parametros'!K$7,1))</f>
+        <v/>
+      </c>
+      <c r="AK116" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL116" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM116" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN116" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Pallet 1200 × 1000 (fracción)</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Embalaje</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>IndusPallets</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$5:$AR$5)*IF($E117="CABA",'Parametros'!B$7,IF($E117="PBA",1-'Parametros'!B$7,1))</f>
+        <v/>
+      </c>
+      <c r="G117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$6:$AR$6)*IF($E117="CABA",'Parametros'!C$7,IF($E117="PBA",1-'Parametros'!C$7,1))</f>
+        <v/>
+      </c>
+      <c r="H117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$7:$AR$7)*IF($E117="CABA",'Parametros'!D$7,IF($E117="PBA",1-'Parametros'!D$7,1))</f>
+        <v/>
+      </c>
+      <c r="I117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$8:$AR$8)*IF($E117="CABA",'Parametros'!E$7,IF($E117="PBA",1-'Parametros'!E$7,1))</f>
+        <v/>
+      </c>
+      <c r="J117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$9:$AR$9)*IF($E117="CABA",'Parametros'!F$7,IF($E117="PBA",1-'Parametros'!F$7,1))</f>
+        <v/>
+      </c>
+      <c r="K117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$10:$AR$10)*IF($E117="CABA",'Parametros'!G$7,IF($E117="PBA",1-'Parametros'!G$7,1))</f>
+        <v/>
+      </c>
+      <c r="L117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$11:$AR$11)*IF($E117="CABA",'Parametros'!H$7,IF($E117="PBA",1-'Parametros'!H$7,1))</f>
+        <v/>
+      </c>
+      <c r="M117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$12:$AR$12)*IF($E117="CABA",'Parametros'!I$7,IF($E117="PBA",1-'Parametros'!I$7,1))</f>
+        <v/>
+      </c>
+      <c r="N117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$13:$AR$13)*IF($E117="CABA",'Parametros'!J$7,IF($E117="PBA",1-'Parametros'!J$7,1))</f>
+        <v/>
+      </c>
+      <c r="O117" s="21">
+        <f>SUMPRODUCT($AK117:$AR117,$AK$14:$AR$14)*IF($E117="CABA",'Parametros'!K$7,IF($E117="PBA",1-'Parametros'!K$7,1))</f>
+        <v/>
+      </c>
+      <c r="AK117" s="22" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="AL117" s="22" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="AM117" s="22" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="AN117" s="22" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="AO117" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP117" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ117" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR117" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A16:E113"/>
+  <autoFilter ref="A16:E117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
